--- a/database/event/4500/event_4500_evp_summary.xlsx
+++ b/database/event/4500/event_4500_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9002</v>
+        <v>7.0789</v>
       </c>
       <c r="C2" t="n">
-        <v>1.681</v>
+        <v>1.7245</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3662</v>
+        <v>2.3763</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9002</v>
+        <v>7.0789</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6876</v>
+        <v>4.8663</v>
       </c>
       <c r="G2" t="n">
         <v>2.2126</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2989</v>
+        <v>7.9699</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1054</v>
+        <v>6.4598</v>
       </c>
       <c r="J2" t="n">
         <v>2.2126</v>
@@ -529,7 +529,7 @@
         <v>105</v>
       </c>
       <c r="M2" t="n">
-        <v>7.318000000000001</v>
+        <v>8.6724</v>
       </c>
       <c r="N2" t="n">
         <v>228</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9406</v>
+        <v>6.2475</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4472</v>
+        <v>1.522</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9785</v>
+        <v>2.0451</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9406</v>
+        <v>6.2475</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9753</v>
+        <v>3.1417</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9653</v>
+        <v>3.1058</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9753</v>
+        <v>3.1417</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4115</v>
+        <v>2.5464</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9653</v>
+        <v>3.1058</v>
       </c>
       <c r="K3" t="n">
         <v>123</v>
@@ -575,7 +575,7 @@
         <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3768</v>
+        <v>5.652200000000001</v>
       </c>
       <c r="N3" t="n">
         <v>228</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9307</v>
+        <v>6.1498</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4448</v>
+        <v>1.4982</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9745</v>
+        <v>2.0062</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9307</v>
+        <v>6.1498</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8249</v>
+        <v>3.1845</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1058</v>
+        <v>2.9653</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8249</v>
+        <v>3.1845</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2896</v>
+        <v>2.5811</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1058</v>
+        <v>2.9653</v>
       </c>
       <c r="K4" t="n">
         <v>123</v>
@@ -621,7 +621,7 @@
         <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3954</v>
+        <v>5.5464</v>
       </c>
       <c r="N4" t="n">
         <v>228</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8406</v>
+        <v>4.1049</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9356</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1302</v>
+        <v>1.1915</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8406</v>
+        <v>4.1049</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5805</v>
+        <v>1.8447</v>
       </c>
       <c r="G5" t="n">
         <v>2.2601</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5805</v>
+        <v>1.8447</v>
       </c>
       <c r="I5" t="n">
-        <v>1.281</v>
+        <v>1.4952</v>
       </c>
       <c r="J5" t="n">
         <v>2.2601</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5411</v>
+        <v>3.7553</v>
       </c>
       <c r="N5" t="n">
         <v>234</v>
@@ -676,323 +676,323 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7064</v>
+        <v>3.0725</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6593</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.672</v>
+        <v>0.7802</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7064</v>
+        <v>3.0725</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3317</v>
+        <v>1.9116</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3747</v>
+        <v>1.1609</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3317</v>
+        <v>1.9116</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0794</v>
+        <v>1.5494</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3747</v>
+        <v>1.1609</v>
       </c>
       <c r="K6" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L6" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4541</v>
+        <v>2.7103</v>
       </c>
       <c r="N6" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6777</v>
+        <v>2.7064</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6523</v>
+        <v>0.6593</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6604</v>
+        <v>0.6343</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6777</v>
+        <v>2.7064</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5168</v>
+        <v>1.3317</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1609</v>
+        <v>1.3747</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5168</v>
+        <v>1.3317</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2294</v>
+        <v>1.0794</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1609</v>
+        <v>1.3747</v>
       </c>
       <c r="K7" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="L7" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3903</v>
+        <v>2.4541</v>
       </c>
       <c r="N7" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.1946</v>
+        <v>2.2533</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5346</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4652</v>
+        <v>0.4538</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1946</v>
+        <v>2.2533</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1946</v>
+        <v>3.0135</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1946</v>
+        <v>3.0135</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1946</v>
+        <v>2.4425</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="K8" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1946</v>
+        <v>1.6823</v>
       </c>
       <c r="N8" t="n">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.16</v>
+        <v>2.1966</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5262</v>
+        <v>0.5351</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4512</v>
+        <v>0.4312</v>
       </c>
       <c r="E9" t="n">
-        <v>2.16</v>
+        <v>2.1966</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4233</v>
+        <v>2.1966</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7367</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4233</v>
+        <v>2.1966</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1536</v>
+        <v>2.1966</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7367</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="L9" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8903</v>
+        <v>2.1966</v>
       </c>
       <c r="N9" t="n">
-        <v>234</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7041</v>
+        <v>2.16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4151</v>
+        <v>0.5262</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2671</v>
+        <v>0.4166</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7041</v>
+        <v>2.16</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4643</v>
+        <v>1.4233</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7602</v>
+        <v>0.7367</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4643</v>
+        <v>1.4233</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9974</v>
+        <v>1.1536</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7602</v>
+        <v>0.7367</v>
       </c>
       <c r="K10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L10" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2372</v>
+        <v>1.8903</v>
       </c>
       <c r="N10" t="n">
-        <v>180</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5744</v>
+        <v>1.5759</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3835</v>
+        <v>0.3839</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2147</v>
+        <v>0.1839</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5744</v>
+        <v>1.5759</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5744</v>
+        <v>0.4423</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.1336</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5744</v>
+        <v>0.4423</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5744</v>
+        <v>0.3585</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.1336</v>
       </c>
       <c r="K11" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5744</v>
+        <v>1.4921</v>
       </c>
       <c r="N11" t="n">
-        <v>143</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3699</v>
+        <v>1.5744</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3337</v>
+        <v>0.3835</v>
       </c>
       <c r="D12" t="n">
-        <v>0.132</v>
+        <v>0.1833</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3699</v>
+        <v>1.5744</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2363</v>
+        <v>1.5744</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1336</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2363</v>
+        <v>1.5744</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1915</v>
+        <v>1.5744</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1336</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3251</v>
+        <v>1.5744</v>
       </c>
       <c r="N12" t="n">
-        <v>234</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.166</v>
+        <v>1.4517</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2841</v>
+        <v>0.3537</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0497</v>
+        <v>0.1344</v>
       </c>
       <c r="E13" t="n">
-        <v>1.166</v>
+        <v>1.4517</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9779</v>
+        <v>2.2636</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8119</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9779</v>
+        <v>2.2636</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6031</v>
+        <v>1.8347</v>
       </c>
       <c r="J13" t="n">
         <v>-0.8119</v>
@@ -1035,7 +1035,7 @@
         <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7912</v>
+        <v>1.0228</v>
       </c>
       <c r="N13" t="n">
         <v>180</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0875</v>
+        <v>1.3288</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2649</v>
+        <v>0.3237</v>
       </c>
       <c r="D14" t="n">
-        <v>0.018</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0875</v>
+        <v>1.3288</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0875</v>
+        <v>1.3288</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0875</v>
+        <v>1.3288</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0875</v>
+        <v>1.3288</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0875</v>
+        <v>1.3288</v>
       </c>
       <c r="N14" t="n">
         <v>143</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.859</v>
+        <v>0.9889</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2093</v>
+        <v>0.2409</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0743</v>
+        <v>-0.0499</v>
       </c>
       <c r="E15" t="n">
-        <v>0.859</v>
+        <v>0.9889</v>
       </c>
       <c r="F15" t="n">
-        <v>0.859</v>
+        <v>0.9889</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.859</v>
+        <v>0.9889</v>
       </c>
       <c r="I15" t="n">
-        <v>0.859</v>
+        <v>0.9889</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.859</v>
+        <v>0.9889</v>
       </c>
       <c r="N15" t="n">
         <v>139</v>
@@ -1146,7 +1146,7 @@
         <v>0.1491</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1742</v>
+        <v>-0.2001</v>
       </c>
       <c r="E16" t="n">
         <v>0.6119</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3267</v>
+        <v>0.3963</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0796</v>
+        <v>0.0965</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2894</v>
+        <v>-0.286</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3267</v>
+        <v>0.3963</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2111</v>
+        <v>0.2807</v>
       </c>
       <c r="G17" t="n">
         <v>0.1156</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2111</v>
+        <v>0.2807</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1711</v>
+        <v>0.2275</v>
       </c>
       <c r="J17" t="n">
         <v>0.1156</v>
@@ -1219,7 +1219,7 @@
         <v>105</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2867</v>
+        <v>0.3431</v>
       </c>
       <c r="N17" t="n">
         <v>228</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2389</v>
+        <v>0.3309</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0582</v>
+        <v>0.0806</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3249</v>
+        <v>-0.3121</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2389</v>
+        <v>0.3309</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5538</v>
+        <v>0.6458</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3149</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5538</v>
+        <v>0.6458</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4489</v>
+        <v>0.5234</v>
       </c>
       <c r="J18" t="n">
         <v>-0.3149</v>
@@ -1265,7 +1265,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>0.134</v>
+        <v>0.2085</v>
       </c>
       <c r="N18" t="n">
         <v>194</v>
@@ -1284,7 +1284,7 @@
         <v>0.0225</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.384</v>
+        <v>-0.4071</v>
       </c>
       <c r="E19" t="n">
         <v>0.0925</v>
@@ -1330,7 +1330,7 @@
         <v>-0.0169</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4494</v>
+        <v>-0.4716</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0694</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1605</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0391</v>
+        <v>-0.0227</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4862</v>
+        <v>-0.481</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1605</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1605</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1605</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1605</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1605</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="N21" t="n">
         <v>139</v>
@@ -1422,7 +1422,7 @@
         <v>-0.1035</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5929</v>
+        <v>-0.6131</v>
       </c>
       <c r="E22" t="n">
         <v>-0.4247</v>
@@ -1468,7 +1468,7 @@
         <v>-0.1167</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6149</v>
+        <v>-0.6348</v>
       </c>
       <c r="E23" t="n">
         <v>-0.4791</v>
@@ -1514,7 +1514,7 @@
         <v>-0.1803</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7204</v>
+        <v>-0.7388</v>
       </c>
       <c r="E24" t="n">
         <v>-0.7402</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.9523</v>
+        <v>-0.8849</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.232</v>
+        <v>-0.2156</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8061</v>
+        <v>-0.7965</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9523</v>
+        <v>-0.8849</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2849</v>
+        <v>-0.2175</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6674</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2849</v>
+        <v>-0.2175</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2309</v>
+        <v>-0.1763</v>
       </c>
       <c r="J25" t="n">
         <v>-0.6674</v>
@@ -1587,7 +1587,7 @@
         <v>50</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8983</v>
+        <v>-0.8437</v>
       </c>
       <c r="N25" t="n">
         <v>180</v>
@@ -1606,7 +1606,7 @@
         <v>-0.3151</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9439</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="E26" t="n">
         <v>-1.2934</v>
@@ -1652,7 +1652,7 @@
         <v>-0.3514</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.0041</v>
+        <v>-1.0186</v>
       </c>
       <c r="E27" t="n">
         <v>-1.4424</v>
@@ -1698,7 +1698,7 @@
         <v>-0.3517</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0046</v>
+        <v>-1.0191</v>
       </c>
       <c r="E28" t="n">
         <v>-1.4437</v>
@@ -1744,7 +1744,7 @@
         <v>-0.4713</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.203</v>
+        <v>-1.2147</v>
       </c>
       <c r="E29" t="n">
         <v>-1.9348</v>
@@ -1790,7 +1790,7 @@
         <v>-0.6447000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.4905</v>
+        <v>-1.4983</v>
       </c>
       <c r="E30" t="n">
         <v>-2.6465</v>
@@ -1836,7 +1836,7 @@
         <v>-0.7285</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.6295</v>
+        <v>-1.6353</v>
       </c>
       <c r="E31" t="n">
         <v>-2.9905</v>

--- a/database/event/4500/event_4500_evp_summary.xlsx
+++ b/database/event/4500/event_4500_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0789</v>
+        <v>6.3249</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7245</v>
+        <v>1.5408</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3763</v>
+        <v>2.2174</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0789</v>
+        <v>6.3249</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8663</v>
+        <v>4.4518</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2126</v>
+        <v>1.8731</v>
       </c>
       <c r="H2" t="n">
-        <v>7.9699</v>
+        <v>11.0583</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4598</v>
+        <v>5.7498</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2126</v>
+        <v>1.8731</v>
       </c>
       <c r="K2" t="n">
         <v>123</v>
@@ -529,7 +529,7 @@
         <v>105</v>
       </c>
       <c r="M2" t="n">
-        <v>8.6724</v>
+        <v>7.6229</v>
       </c>
       <c r="N2" t="n">
         <v>228</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2475</v>
+        <v>5.876</v>
       </c>
       <c r="C3" t="n">
-        <v>1.522</v>
+        <v>1.4315</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0451</v>
+        <v>2.0147</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2475</v>
+        <v>5.876</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1417</v>
+        <v>3.082</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1058</v>
+        <v>2.794</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1417</v>
+        <v>5.3728</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5464</v>
+        <v>2.7936</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1058</v>
+        <v>2.794</v>
       </c>
       <c r="K3" t="n">
         <v>123</v>
@@ -575,7 +575,7 @@
         <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>5.652200000000001</v>
+        <v>5.5876</v>
       </c>
       <c r="N3" t="n">
         <v>228</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1498</v>
+        <v>5.5984</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4982</v>
+        <v>1.3639</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0062</v>
+        <v>1.8894</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1498</v>
+        <v>5.5984</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1845</v>
+        <v>3.0107</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9653</v>
+        <v>2.5877</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1845</v>
+        <v>5.1214</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5811</v>
+        <v>2.6629</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9653</v>
+        <v>2.5877</v>
       </c>
       <c r="K4" t="n">
         <v>123</v>
@@ -621,7 +621,7 @@
         <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5464</v>
+        <v>5.2506</v>
       </c>
       <c r="N4" t="n">
         <v>228</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1049</v>
+        <v>4.4094</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.0742</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1915</v>
+        <v>1.3526</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1049</v>
+        <v>4.4094</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8447</v>
+        <v>2.4422</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2601</v>
+        <v>1.9673</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8447</v>
+        <v>3.1184</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4952</v>
+        <v>1.6214</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2601</v>
+        <v>1.9673</v>
       </c>
       <c r="K5" t="n">
         <v>133</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7553</v>
+        <v>3.5887</v>
       </c>
       <c r="N5" t="n">
         <v>234</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0725</v>
+        <v>3.6642</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.8927</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7802</v>
+        <v>1.0162</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0725</v>
+        <v>3.6642</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9116</v>
+        <v>2.526</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1609</v>
+        <v>1.1382</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9116</v>
+        <v>3.4138</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5494</v>
+        <v>1.775</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1609</v>
+        <v>1.1382</v>
       </c>
       <c r="K6" t="n">
         <v>133</v>
@@ -713,7 +713,7 @@
         <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7103</v>
+        <v>2.9132</v>
       </c>
       <c r="N6" t="n">
         <v>234</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7064</v>
+        <v>3.466</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6593</v>
+        <v>0.8444</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6343</v>
+        <v>0.9267</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7064</v>
+        <v>3.466</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3317</v>
+        <v>2.3321</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3747</v>
+        <v>1.1339</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3317</v>
+        <v>2.7306</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0794</v>
+        <v>1.4198</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3747</v>
+        <v>1.1339</v>
       </c>
       <c r="K7" t="n">
         <v>123</v>
@@ -759,7 +759,7 @@
         <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4541</v>
+        <v>2.5537</v>
       </c>
       <c r="N7" t="n">
         <v>228</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2533</v>
+        <v>2.9184</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4538</v>
+        <v>0.6795</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2533</v>
+        <v>2.9184</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0135</v>
+        <v>2.291</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7602</v>
+        <v>0.6274</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0135</v>
+        <v>2.5858</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4425</v>
+        <v>1.3445</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7602</v>
+        <v>0.6274</v>
       </c>
       <c r="K8" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6823</v>
+        <v>1.9719</v>
       </c>
       <c r="N8" t="n">
-        <v>180</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1966</v>
+        <v>2.5132</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5351</v>
+        <v>0.6123</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4312</v>
+        <v>0.4966</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1966</v>
+        <v>2.5132</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1966</v>
+        <v>3.0221</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.5089</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1966</v>
+        <v>5.1617</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1966</v>
+        <v>2.6839</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.5089</v>
       </c>
       <c r="K9" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1966</v>
+        <v>2.175</v>
       </c>
       <c r="N9" t="n">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.16</v>
+        <v>2.4103</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5262</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4166</v>
+        <v>0.4501</v>
       </c>
       <c r="E10" t="n">
-        <v>2.16</v>
+        <v>2.4103</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4233</v>
+        <v>2.4103</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7367</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4233</v>
+        <v>2.4103</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1536</v>
+        <v>2.4103</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7367</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="L10" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8903</v>
+        <v>2.4103</v>
       </c>
       <c r="N10" t="n">
-        <v>234</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5759</v>
+        <v>2.1683</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3839</v>
+        <v>0.5282</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1839</v>
+        <v>0.3409</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5759</v>
+        <v>2.1683</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4423</v>
+        <v>1.2211</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1336</v>
+        <v>0.9472</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4423</v>
+        <v>1.2211</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3585</v>
+        <v>0.6349</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1336</v>
+        <v>0.9472</v>
       </c>
       <c r="K11" t="n">
         <v>133</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4921</v>
+        <v>1.5821</v>
       </c>
       <c r="N11" t="n">
         <v>234</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5744</v>
+        <v>2.1051</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3835</v>
+        <v>0.5128</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1833</v>
+        <v>0.3123</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5744</v>
+        <v>2.1051</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5744</v>
+        <v>2.6495</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.5444</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5744</v>
+        <v>3.849</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5744</v>
+        <v>2.0013</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.5444</v>
       </c>
       <c r="K12" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5744</v>
+        <v>1.4569</v>
       </c>
       <c r="N12" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4517</v>
+        <v>1.9592</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3537</v>
+        <v>0.4773</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1344</v>
+        <v>0.2465</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4517</v>
+        <v>1.9592</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2636</v>
+        <v>1.9592</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8119</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2636</v>
+        <v>1.9592</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8347</v>
+        <v>1.9592</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8119</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0228</v>
+        <v>1.9592</v>
       </c>
       <c r="N13" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3288</v>
+        <v>1.7556</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3237</v>
+        <v>0.4277</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1546</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3288</v>
+        <v>1.7556</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3288</v>
+        <v>1.7556</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3288</v>
+        <v>1.7556</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3288</v>
+        <v>1.7556</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3288</v>
+        <v>1.7556</v>
       </c>
       <c r="N14" t="n">
         <v>143</v>
@@ -1090,541 +1090,541 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>TenZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9889</v>
+        <v>1.5735</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2409</v>
+        <v>0.3833</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0499</v>
+        <v>0.0723</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9889</v>
+        <v>1.5735</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9889</v>
+        <v>1.6928</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.1193</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9889</v>
+        <v>1.6928</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9889</v>
+        <v>0.8802</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.1193</v>
       </c>
       <c r="K15" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9889</v>
+        <v>0.7609</v>
       </c>
       <c r="N15" t="n">
-        <v>139</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TenZ</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6119</v>
+        <v>1.3676</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1491</v>
+        <v>0.3332</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2001</v>
+        <v>-0.0206</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6119</v>
+        <v>1.3676</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7731</v>
+        <v>0.9607</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1612</v>
+        <v>0.4069</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7731</v>
+        <v>0.9607</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6266</v>
+        <v>0.4995</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1612</v>
+        <v>0.4069</v>
       </c>
       <c r="K16" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="L16" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4654</v>
+        <v>0.9064</v>
       </c>
       <c r="N16" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3963</v>
+        <v>1.3419</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0965</v>
+        <v>0.3269</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.286</v>
+        <v>-0.0322</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3963</v>
+        <v>1.3419</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2807</v>
+        <v>1.5661</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1156</v>
+        <v>-0.2242</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2807</v>
+        <v>1.5661</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2275</v>
+        <v>0.8143</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1156</v>
+        <v>-0.2242</v>
       </c>
       <c r="K17" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="L17" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3431</v>
+        <v>0.5901000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>228</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3309</v>
+        <v>1.1796</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0806</v>
+        <v>0.2874</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3121</v>
+        <v>-0.1055</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3309</v>
+        <v>1.1796</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6458</v>
+        <v>1.1796</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3149</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6458</v>
+        <v>1.1796</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5234</v>
+        <v>1.1796</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3149</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2085</v>
+        <v>1.1796</v>
       </c>
       <c r="N18" t="n">
-        <v>194</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0925</v>
+        <v>0.8314</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0225</v>
+        <v>0.2025</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4071</v>
+        <v>-0.2627</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0925</v>
+        <v>0.8314</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0925</v>
+        <v>0.882</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.0506</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0925</v>
+        <v>0.882</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0925</v>
+        <v>0.4586</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.0506</v>
       </c>
       <c r="K19" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0925</v>
+        <v>0.408</v>
       </c>
       <c r="N19" t="n">
-        <v>143</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0694</v>
+        <v>0.3543</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0169</v>
+        <v>0.0863</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4716</v>
+        <v>-0.4781</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0694</v>
+        <v>0.3543</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1435</v>
+        <v>0.3543</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2129</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1435</v>
+        <v>0.3543</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1163</v>
+        <v>0.3543</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2129</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.3543</v>
       </c>
       <c r="N20" t="n">
-        <v>194</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0227</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.481</v>
+        <v>-0.4868</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="N21" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4247</v>
+        <v>0.0764</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1035</v>
+        <v>0.0186</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6131</v>
+        <v>-0.6035</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4247</v>
+        <v>0.0764</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4247</v>
+        <v>0.5556</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.4792</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4247</v>
+        <v>0.5556</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4247</v>
+        <v>0.2889</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.4792</v>
       </c>
       <c r="K22" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4247</v>
+        <v>-0.1903</v>
       </c>
       <c r="N22" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4791</v>
+        <v>-0.119</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1167</v>
+        <v>-0.029</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6348</v>
+        <v>-0.6917</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4791</v>
+        <v>-0.119</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4791</v>
+        <v>-0.2091</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.0901</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4791</v>
+        <v>-0.2091</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4791</v>
+        <v>-0.1087</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.0901</v>
       </c>
       <c r="K23" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4791</v>
+        <v>-0.01860000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.7402</v>
+        <v>-0.1315</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1803</v>
+        <v>-0.032</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7388</v>
+        <v>-0.6974</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7402</v>
+        <v>-0.1315</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.1315</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0935</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.1315</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5242</v>
+        <v>-0.1315</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0935</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="L24" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6177</v>
+        <v>-0.1315</v>
       </c>
       <c r="N24" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.8849</v>
+        <v>-0.1319</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2156</v>
+        <v>-0.0321</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7965</v>
+        <v>-0.6976</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8849</v>
+        <v>-0.1319</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2175</v>
+        <v>-0.1319</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6674</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2175</v>
+        <v>-0.1319</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1763</v>
+        <v>-0.1319</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6674</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L25" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8437</v>
+        <v>-0.1319</v>
       </c>
       <c r="N25" t="n">
-        <v>180</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.2934</v>
+        <v>-0.9278</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3151</v>
+        <v>-0.226</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-1.0569</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2934</v>
+        <v>-0.9278</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0989</v>
+        <v>-0.7856</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1945</v>
+        <v>-0.1422</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0989</v>
+        <v>-0.7856</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8907</v>
+        <v>-0.4085</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1945</v>
+        <v>-0.1422</v>
       </c>
       <c r="K26" t="n">
         <v>140</v>
@@ -1633,7 +1633,7 @@
         <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.0852</v>
+        <v>-0.5507</v>
       </c>
       <c r="N26" t="n">
         <v>194</v>
@@ -1642,35 +1642,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.4424</v>
+        <v>-1.1954</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3514</v>
+        <v>-0.2912</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.0186</v>
+        <v>-1.1777</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.4424</v>
+        <v>-1.1954</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0415</v>
+        <v>-1.1747</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4009</v>
+        <v>-0.0207</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.0415</v>
+        <v>-1.1747</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8442</v>
+        <v>-0.6108</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4009</v>
+        <v>-0.0207</v>
       </c>
       <c r="K27" t="n">
         <v>140</v>
@@ -1679,7 +1679,7 @@
         <v>54</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.2451</v>
+        <v>-0.6315000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>194</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.4437</v>
+        <v>-1.2093</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3517</v>
+        <v>-0.2946</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0191</v>
+        <v>-1.184</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.4437</v>
+        <v>-1.2093</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.9499</v>
+        <v>-1.2093</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4938</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9499</v>
+        <v>-1.2093</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7699</v>
+        <v>-1.2093</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4938</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L28" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.2637</v>
+        <v>-1.2093</v>
       </c>
       <c r="N28" t="n">
-        <v>180</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.9348</v>
+        <v>-1.346</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4713</v>
+        <v>-0.3279</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2147</v>
+        <v>-1.2457</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.9348</v>
+        <v>-1.346</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.9348</v>
+        <v>-0.9845</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.3615</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.9348</v>
+        <v>-0.9845</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.9348</v>
+        <v>-0.5119</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.3615</v>
       </c>
       <c r="K29" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.9348</v>
+        <v>-0.8734</v>
       </c>
       <c r="N29" t="n">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.6465</v>
+        <v>-2.0463</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.4985</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.4983</v>
+        <v>-1.5618</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.6465</v>
+        <v>-2.0463</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.6465</v>
+        <v>-2.0463</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.6465</v>
+        <v>-2.0463</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.6465</v>
+        <v>-2.0463</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.6465</v>
+        <v>-2.0463</v>
       </c>
       <c r="N30" t="n">
         <v>143</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.9905</v>
+        <v>-2.7329</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.7285</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.6353</v>
+        <v>-1.8718</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.9905</v>
+        <v>-2.7329</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.0558</v>
+        <v>-2.1742</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.9347</v>
+        <v>-0.5587</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.0558</v>
+        <v>-2.1742</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.6663</v>
+        <v>-1.1305</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9347</v>
+        <v>-0.5587</v>
       </c>
       <c r="K31" t="n">
         <v>133</v>
@@ -1863,7 +1863,7 @@
         <v>101</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.601</v>
+        <v>-1.6892</v>
       </c>
       <c r="N31" t="n">
         <v>234</v>
@@ -1969,10 +1969,10 @@
         <v>1.44</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1243</v>
+        <v>1.0754</v>
       </c>
       <c r="J2" t="n">
-        <v>32.6047</v>
+        <v>31.1866</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7725</v>
+        <v>0.7611</v>
       </c>
       <c r="J3" t="n">
-        <v>22.4025</v>
+        <v>22.0719</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2629</v>
+        <v>0.3135</v>
       </c>
       <c r="J4" t="n">
-        <v>7.6241</v>
+        <v>9.0915</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0452</v>
+        <v>0.0185</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3108</v>
+        <v>0.5365</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.93</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3741</v>
+        <v>-0.3016</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.8489</v>
+        <v>-8.7464</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3906</v>
+        <v>0.4453</v>
       </c>
       <c r="J7" t="n">
-        <v>11.3274</v>
+        <v>12.9137</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3316</v>
+        <v>0.3701</v>
       </c>
       <c r="J8" t="n">
-        <v>9.616400000000001</v>
+        <v>10.7329</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.93</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1666</v>
+        <v>-0.098</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.8314</v>
+        <v>-2.842</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3035</v>
+        <v>-0.1856</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.801500000000001</v>
+        <v>-5.3824</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4356</v>
+        <v>-0.2762</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.6324</v>
+        <v>-8.0098</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>2.18</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1443</v>
+        <v>1.8681</v>
       </c>
       <c r="J12" t="n">
-        <v>47.1746</v>
+        <v>41.0982</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.38</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8158</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>17.9476</v>
+        <v>20.3258</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6357</v>
+        <v>0.7493</v>
       </c>
       <c r="J14" t="n">
-        <v>13.9854</v>
+        <v>16.4846</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.24</v>
       </c>
       <c r="I15" t="n">
-        <v>0.499</v>
+        <v>0.6099</v>
       </c>
       <c r="J15" t="n">
-        <v>10.978</v>
+        <v>13.4178</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>1.07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0703</v>
+        <v>0.1614</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5466</v>
+        <v>3.5508</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>0.89</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0808</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7776</v>
+        <v>-2.0504</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.212</v>
+        <v>-0.1843</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.664</v>
+        <v>-4.0546</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4721</v>
+        <v>-0.3304</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.3862</v>
+        <v>-7.2688</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.61</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5522</v>
+        <v>-0.3763</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.1484</v>
+        <v>-8.278600000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.42</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8085</v>
+        <v>-0.5542</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.787</v>
+        <v>-12.1924</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.61</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3294</v>
+        <v>0.9571</v>
       </c>
       <c r="J22" t="n">
-        <v>30.5762</v>
+        <v>22.0133</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.58</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2708</v>
+        <v>0.9216</v>
       </c>
       <c r="J23" t="n">
-        <v>29.2284</v>
+        <v>21.1968</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.44</v>
       </c>
       <c r="I24" t="n">
-        <v>0.97</v>
+        <v>0.7548</v>
       </c>
       <c r="J24" t="n">
-        <v>22.31</v>
+        <v>17.3604</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.4</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8632</v>
+        <v>0.7071</v>
       </c>
       <c r="J25" t="n">
-        <v>19.8536</v>
+        <v>16.2633</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.13</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2337</v>
+        <v>0.3297</v>
       </c>
       <c r="J26" t="n">
-        <v>5.3751</v>
+        <v>7.5831</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1074</v>
+        <v>-0.1127</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.4702</v>
+        <v>-2.5921</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2206</v>
+        <v>-0.1914</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.0738</v>
+        <v>-4.4022</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.59</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5756</v>
+        <v>-0.3925</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.2388</v>
+        <v>-9.0275</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.54</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6472</v>
+        <v>-0.4392</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.8856</v>
+        <v>-10.1016</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6746</v>
+        <v>-0.4579</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.5158</v>
+        <v>-10.5317</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.72</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6402</v>
+        <v>1.1441</v>
       </c>
       <c r="J32" t="n">
-        <v>44.2854</v>
+        <v>30.8907</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4073</v>
+        <v>0.4101</v>
       </c>
       <c r="J33" t="n">
-        <v>10.9971</v>
+        <v>11.0727</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3792</v>
+        <v>0.395</v>
       </c>
       <c r="J34" t="n">
-        <v>10.2384</v>
+        <v>10.665</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.08</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1781</v>
+        <v>0.2453</v>
       </c>
       <c r="J35" t="n">
-        <v>4.8087</v>
+        <v>6.6231</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.3019</v>
+        <v>-12.42</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.33</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="J37" t="n">
-        <v>15.6897</v>
+        <v>14.796</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.92</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1647</v>
+        <v>-0.1052</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.4469</v>
+        <v>-2.8404</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.91</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1846</v>
+        <v>-0.1164</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.9842</v>
+        <v>-3.1428</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.86</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2732</v>
+        <v>-0.1701</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.3764</v>
+        <v>-4.5927</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.66</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.3665</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.12</v>
+        <v>-9.8955</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.75</v>
       </c>
       <c r="I42" t="n">
-        <v>1.6335</v>
+        <v>1.1431</v>
       </c>
       <c r="J42" t="n">
-        <v>39.204</v>
+        <v>27.4344</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.68</v>
       </c>
       <c r="I43" t="n">
-        <v>1.5067</v>
+        <v>1.0597</v>
       </c>
       <c r="J43" t="n">
-        <v>36.1608</v>
+        <v>25.4328</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2118</v>
+        <v>0.3003</v>
       </c>
       <c r="J44" t="n">
-        <v>5.0832</v>
+        <v>7.2072</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0989</v>
+        <v>0.1841</v>
       </c>
       <c r="J45" t="n">
-        <v>2.3736</v>
+        <v>4.4184</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0054</v>
+        <v>0.0882</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1296</v>
+        <v>2.1168</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>0.96</v>
       </c>
       <c r="I47" t="n">
-        <v>0.012</v>
+        <v>-0.0255</v>
       </c>
       <c r="J47" t="n">
-        <v>0.288</v>
+        <v>-0.612</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>0.84</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2016</v>
+        <v>-0.1689</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.8384</v>
+        <v>-4.0536</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.72</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4187</v>
+        <v>-0.2853</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.0488</v>
+        <v>-6.8472</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4349</v>
+        <v>-0.2946</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.4376</v>
+        <v>-7.0704</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6742</v>
+        <v>-0.4539</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.1808</v>
+        <v>-10.8936</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.52</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3302</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>39.906</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1064</v>
+        <v>0.7852</v>
       </c>
       <c r="J53" t="n">
-        <v>33.192</v>
+        <v>23.556</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.9</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4294</v>
+        <v>-0.3683</v>
       </c>
       <c r="J54" t="n">
-        <v>-12.882</v>
+        <v>-11.049</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.8</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6924</v>
+        <v>-0.641</v>
       </c>
       <c r="J55" t="n">
-        <v>-20.772</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9026</v>
+        <v>-0.8682</v>
       </c>
       <c r="J56" t="n">
-        <v>-27.078</v>
+        <v>-26.046</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2733</v>
+        <v>0.3117</v>
       </c>
       <c r="J57" t="n">
-        <v>8.199</v>
+        <v>9.351000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.12</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2404</v>
+        <v>0.2739</v>
       </c>
       <c r="J58" t="n">
-        <v>7.212</v>
+        <v>8.217000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2058</v>
+        <v>0.2347</v>
       </c>
       <c r="J59" t="n">
-        <v>6.174</v>
+        <v>7.041</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1133</v>
+        <v>-0.0553</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.399</v>
+        <v>-1.659</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1732</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.196</v>
+        <v>-2.814</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5775</v>
+        <v>0.6952</v>
       </c>
       <c r="J62" t="n">
-        <v>17.325</v>
+        <v>20.856</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.02</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0526</v>
+        <v>0.0636</v>
       </c>
       <c r="J63" t="n">
-        <v>1.578</v>
+        <v>1.908</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.101</v>
+        <v>-0.0519</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.03</v>
+        <v>-1.557</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2169</v>
+        <v>-0.1252</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.507</v>
+        <v>-3.756</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3142</v>
+        <v>-0.1902</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.426</v>
+        <v>-5.706</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.27</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7798</v>
+        <v>0.7559</v>
       </c>
       <c r="J67" t="n">
-        <v>23.394</v>
+        <v>22.677</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5555</v>
+        <v>0.5332</v>
       </c>
       <c r="J68" t="n">
-        <v>16.665</v>
+        <v>15.996</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4445</v>
+        <v>0.4298</v>
       </c>
       <c r="J69" t="n">
-        <v>13.335</v>
+        <v>12.894</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2742</v>
+        <v>0.2961</v>
       </c>
       <c r="J70" t="n">
-        <v>8.226000000000001</v>
+        <v>8.882999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6776</v>
+        <v>-0.6232</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.328</v>
+        <v>-18.696</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5457</v>
+        <v>0.6615</v>
       </c>
       <c r="J72" t="n">
-        <v>16.371</v>
+        <v>19.845</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.13</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2269</v>
+        <v>0.2819</v>
       </c>
       <c r="J73" t="n">
-        <v>6.807</v>
+        <v>8.457000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0706</v>
+        <v>0.1214</v>
       </c>
       <c r="J74" t="n">
-        <v>2.118</v>
+        <v>3.642</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0706</v>
+        <v>0.1214</v>
       </c>
       <c r="J75" t="n">
-        <v>2.118</v>
+        <v>3.642</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.02</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0074</v>
+        <v>0.0477</v>
       </c>
       <c r="J76" t="n">
-        <v>0.222</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.25</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4489</v>
+        <v>0.5243</v>
       </c>
       <c r="J77" t="n">
-        <v>13.467</v>
+        <v>15.729</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.11</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2394</v>
+        <v>0.2631</v>
       </c>
       <c r="J78" t="n">
-        <v>7.182</v>
+        <v>7.893</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1289</v>
+        <v>0.1366</v>
       </c>
       <c r="J79" t="n">
-        <v>3.867</v>
+        <v>4.098</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1792</v>
+        <v>-0.1015</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.376</v>
+        <v>-3.045</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4833</v>
+        <v>-0.3092</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.499</v>
+        <v>-9.276</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6456</v>
+        <v>0.6155</v>
       </c>
       <c r="J82" t="n">
-        <v>17.4312</v>
+        <v>16.6185</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.17</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5135</v>
       </c>
       <c r="J83" t="n">
-        <v>14.6286</v>
+        <v>13.8645</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3383</v>
+        <v>0.3267</v>
       </c>
       <c r="J84" t="n">
-        <v>9.1341</v>
+        <v>8.8209</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1875</v>
+        <v>0.2126</v>
       </c>
       <c r="J85" t="n">
-        <v>5.0625</v>
+        <v>5.7402</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5698</v>
+        <v>-0.5111</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.3846</v>
+        <v>-13.7997</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.507</v>
+        <v>0.6027</v>
       </c>
       <c r="J87" t="n">
-        <v>13.689</v>
+        <v>16.2729</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.246</v>
+        <v>0.2769</v>
       </c>
       <c r="J88" t="n">
-        <v>6.642</v>
+        <v>7.4763</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1085</v>
+        <v>-0.0539</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.9295</v>
+        <v>-1.4553</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1498</v>
+        <v>-0.08</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.0446</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3037</v>
+        <v>-0.182</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.1999</v>
+        <v>-4.914</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.29</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5323</v>
+        <v>0.6301</v>
       </c>
       <c r="J92" t="n">
-        <v>13.8398</v>
+        <v>16.3826</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2719</v>
+        <v>0.2881</v>
       </c>
       <c r="J93" t="n">
-        <v>7.0694</v>
+        <v>7.4906</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.83</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3187</v>
+        <v>-0.2001</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.286199999999999</v>
+        <v>-5.2026</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3942</v>
+        <v>-0.2502</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.2492</v>
+        <v>-6.5052</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.63</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5969</v>
+        <v>-0.3936</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.5194</v>
+        <v>-10.2336</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1838</v>
+        <v>1.1139</v>
       </c>
       <c r="J97" t="n">
-        <v>30.7788</v>
+        <v>28.9614</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7937</v>
+        <v>0.7834</v>
       </c>
       <c r="J98" t="n">
-        <v>20.6362</v>
+        <v>20.3684</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.17</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4844</v>
+        <v>0.4942</v>
       </c>
       <c r="J99" t="n">
-        <v>12.5944</v>
+        <v>12.8492</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0338</v>
+        <v>0.0955</v>
       </c>
       <c r="J100" t="n">
-        <v>0.8788</v>
+        <v>2.483</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.82</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6703</v>
+        <v>-0.6122</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.4278</v>
+        <v>-15.9172</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2761</v>
+        <v>-0.2371</v>
       </c>
       <c r="J102" t="n">
-        <v>-5.522</v>
+        <v>-4.742</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.7</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3221</v>
+        <v>-0.2692</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.442</v>
+        <v>-5.384</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.57</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5373</v>
+        <v>-0.3957</v>
       </c>
       <c r="J104" t="n">
-        <v>-10.746</v>
+        <v>-7.914</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.48</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6932</v>
+        <v>-0.4774</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.864</v>
+        <v>-9.548</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.36</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8578</v>
+        <v>-0.5926</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.156</v>
+        <v>-11.852</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.93</v>
       </c>
       <c r="I107" t="n">
-        <v>1.888</v>
+        <v>1.5948</v>
       </c>
       <c r="J107" t="n">
-        <v>37.76</v>
+        <v>31.896</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.2394</v>
+        <v>1.1802</v>
       </c>
       <c r="J108" t="n">
-        <v>24.788</v>
+        <v>23.604</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8719</v>
+        <v>0.9772</v>
       </c>
       <c r="J109" t="n">
-        <v>17.438</v>
+        <v>19.544</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.27</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="J110" t="n">
-        <v>11.2</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1487</v>
+        <v>0.2448</v>
       </c>
       <c r="J111" t="n">
-        <v>2.974</v>
+        <v>4.896</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.26</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4591</v>
+        <v>0.5386</v>
       </c>
       <c r="J112" t="n">
-        <v>12.8548</v>
+        <v>15.0808</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.21</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3896</v>
+        <v>0.4495</v>
       </c>
       <c r="J113" t="n">
-        <v>10.9088</v>
+        <v>12.586</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1638</v>
+        <v>-0.0906</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.5864</v>
+        <v>-2.5368</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.87</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2841</v>
+        <v>-0.1696</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.9548</v>
+        <v>-4.7488</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3304</v>
+        <v>-0.2011</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.251200000000001</v>
+        <v>-5.6308</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.87</v>
+        <v>0.8501</v>
       </c>
       <c r="J117" t="n">
-        <v>24.36</v>
+        <v>23.8028</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.22</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6561</v>
+        <v>0.6323</v>
       </c>
       <c r="J118" t="n">
-        <v>18.3708</v>
+        <v>17.7044</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4116</v>
+        <v>0.4026</v>
       </c>
       <c r="J119" t="n">
-        <v>11.5248</v>
+        <v>11.2728</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0617</v>
+        <v>0.109</v>
       </c>
       <c r="J120" t="n">
-        <v>1.7276</v>
+        <v>3.052</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6542</v>
+        <v>-0.598</v>
       </c>
       <c r="J121" t="n">
-        <v>-18.3176</v>
+        <v>-16.744</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.15</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3449</v>
+        <v>0.3788</v>
       </c>
       <c r="J122" t="n">
-        <v>9.3123</v>
+        <v>10.2276</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.05</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1757</v>
+        <v>0.1653</v>
       </c>
       <c r="J123" t="n">
-        <v>4.7439</v>
+        <v>4.4631</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.341</v>
+        <v>-0.2171</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.207000000000001</v>
+        <v>-5.8617</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.77</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4013</v>
+        <v>-0.2568</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.8351</v>
+        <v>-6.9336</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4585</v>
+        <v>-0.2957</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.3795</v>
+        <v>-7.9839</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.71</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6476</v>
+        <v>1.4225</v>
       </c>
       <c r="J127" t="n">
-        <v>44.4852</v>
+        <v>38.4075</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.13</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3572</v>
+        <v>0.3953</v>
       </c>
       <c r="J128" t="n">
-        <v>9.644399999999999</v>
+        <v>10.6731</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1075</v>
+        <v>0.1651</v>
       </c>
       <c r="J129" t="n">
-        <v>2.9025</v>
+        <v>4.4577</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0375</v>
+        <v>0.0975</v>
       </c>
       <c r="J130" t="n">
-        <v>1.0125</v>
+        <v>2.6325</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.668</v>
+        <v>-0.6101</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.036</v>
+        <v>-16.4727</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.17</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3438</v>
+        <v>0.3866</v>
       </c>
       <c r="J132" t="n">
-        <v>9.6264</v>
+        <v>10.8248</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1975</v>
+        <v>0.2078</v>
       </c>
       <c r="J133" t="n">
-        <v>5.53</v>
+        <v>5.8184</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1793</v>
+        <v>0.1864</v>
       </c>
       <c r="J134" t="n">
-        <v>5.0204</v>
+        <v>5.2192</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3058</v>
+        <v>-0.1866</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.5624</v>
+        <v>-5.2248</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4235</v>
+        <v>-0.2674</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.858</v>
+        <v>-7.4872</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.27</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8375</v>
+        <v>0.8004</v>
       </c>
       <c r="J137" t="n">
-        <v>23.45</v>
+        <v>22.4112</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1203</v>
+        <v>0.094</v>
       </c>
       <c r="J138" t="n">
-        <v>3.3684</v>
+        <v>2.632</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.068</v>
+        <v>-0.053</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.904</v>
+        <v>-1.484</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3341</v>
+        <v>-0.2896</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.354799999999999</v>
+        <v>-8.1088</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6916</v>
+        <v>-0.6465</v>
       </c>
       <c r="J141" t="n">
-        <v>-19.3648</v>
+        <v>-18.102</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.69</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5833</v>
+        <v>1.379</v>
       </c>
       <c r="J142" t="n">
-        <v>37.9992</v>
+        <v>33.096</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4596</v>
+        <v>0.5117</v>
       </c>
       <c r="J143" t="n">
-        <v>11.0304</v>
+        <v>12.2808</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.08</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1754</v>
+        <v>0.2439</v>
       </c>
       <c r="J144" t="n">
-        <v>4.2096</v>
+        <v>5.8536</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.145</v>
+        <v>0.2139</v>
       </c>
       <c r="J145" t="n">
-        <v>3.48</v>
+        <v>5.1336</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1248</v>
+        <v>-0.0496</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.9952</v>
+        <v>-1.1904</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.24</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4747</v>
+        <v>0.5511</v>
       </c>
       <c r="J147" t="n">
-        <v>11.3928</v>
+        <v>13.2264</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.89</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2037</v>
+        <v>-0.1349</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.8888</v>
+        <v>-3.2376</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.87</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2415</v>
+        <v>-0.1559</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.796</v>
+        <v>-3.7416</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.84</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.293</v>
+        <v>-0.1868</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.032</v>
+        <v>-4.4832</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.67</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5399</v>
+        <v>-0.3529</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.9576</v>
+        <v>-8.4696</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.43</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6688</v>
+        <v>0.8205</v>
       </c>
       <c r="J152" t="n">
-        <v>20.064</v>
+        <v>24.615</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.15</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2944</v>
+        <v>0.3344</v>
       </c>
       <c r="J153" t="n">
-        <v>8.832000000000001</v>
+        <v>10.032</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1756</v>
+        <v>0.1967</v>
       </c>
       <c r="J154" t="n">
-        <v>5.268</v>
+        <v>5.901</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.349</v>
+        <v>-0.2132</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.47</v>
+        <v>-6.396</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5142</v>
+        <v>-0.3311</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.426</v>
+        <v>-9.933</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.14</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2985</v>
+        <v>0.3297</v>
       </c>
       <c r="J157" t="n">
-        <v>8.955</v>
+        <v>9.891</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2827</v>
+        <v>0.3102</v>
       </c>
       <c r="J158" t="n">
-        <v>8.481</v>
+        <v>9.305999999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0684</v>
       </c>
       <c r="J159" t="n">
-        <v>2.262</v>
+        <v>2.052</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.86</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2895</v>
+        <v>-0.1758</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.685</v>
+        <v>-5.274</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.78</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4089</v>
+        <v>-0.2573</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.267</v>
+        <v>-7.719</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8485</v>
+        <v>0.8449</v>
       </c>
       <c r="J162" t="n">
-        <v>21.2125</v>
+        <v>21.1225</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6563</v>
+        <v>0.6581</v>
       </c>
       <c r="J163" t="n">
-        <v>16.4075</v>
+        <v>16.4525</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.19</v>
       </c>
       <c r="I164" t="n">
-        <v>0.519</v>
+        <v>0.5387</v>
       </c>
       <c r="J164" t="n">
-        <v>12.975</v>
+        <v>13.4675</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.1</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2455</v>
+        <v>0.3067</v>
       </c>
       <c r="J165" t="n">
-        <v>6.1375</v>
+        <v>7.6675</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1237</v>
+        <v>0.1885</v>
       </c>
       <c r="J166" t="n">
-        <v>3.0925</v>
+        <v>4.7125</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.48</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7448</v>
+        <v>0.9254</v>
       </c>
       <c r="J167" t="n">
-        <v>18.62</v>
+        <v>23.135</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1505</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.7625</v>
+        <v>-2.1725</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.92</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1884</v>
+        <v>-0.1104</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.71</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3662</v>
+        <v>-0.2276</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.154999999999999</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3952</v>
+        <v>-0.2476</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.880000000000001</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.5</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2722</v>
+        <v>1.1689</v>
       </c>
       <c r="J172" t="n">
-        <v>38.166</v>
+        <v>35.067</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.05</v>
       </c>
       <c r="I173" t="n">
-        <v>0.134</v>
+        <v>0.1762</v>
       </c>
       <c r="J173" t="n">
-        <v>4.02</v>
+        <v>5.286</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0617</v>
+        <v>0.109</v>
       </c>
       <c r="J174" t="n">
-        <v>1.851</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.97</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2218</v>
+        <v>-0.1565</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.654</v>
+        <v>-4.695</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2575</v>
+        <v>-0.1914</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.725</v>
+        <v>-5.742</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7752</v>
+        <v>0.9646</v>
       </c>
       <c r="J177" t="n">
-        <v>23.256</v>
+        <v>28.938</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3395</v>
+        <v>0.3829</v>
       </c>
       <c r="J178" t="n">
-        <v>10.185</v>
+        <v>11.487</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1553</v>
+        <v>0.1618</v>
       </c>
       <c r="J179" t="n">
-        <v>4.659</v>
+        <v>4.854</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.91</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2105</v>
+        <v>-0.123</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.315</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.35</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.9303</v>
+        <v>-0.6509</v>
       </c>
       <c r="J181" t="n">
-        <v>-27.909</v>
+        <v>-19.527</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.81</v>
       </c>
       <c r="I182" t="n">
-        <v>1.7518</v>
+        <v>1.4947</v>
       </c>
       <c r="J182" t="n">
-        <v>42.0432</v>
+        <v>35.8728</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.33</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7976</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>19.1424</v>
+        <v>20.0928</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.604</v>
+        <v>0.6832</v>
       </c>
       <c r="J184" t="n">
-        <v>14.496</v>
+        <v>16.3968</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1652</v>
+        <v>0.2495</v>
       </c>
       <c r="J185" t="n">
-        <v>3.9648</v>
+        <v>5.988</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.0211</v>
+        <v>0.0594</v>
       </c>
       <c r="J186" t="n">
-        <v>-0.5064</v>
+        <v>1.4256</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.06</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2292</v>
+        <v>0.223</v>
       </c>
       <c r="J187" t="n">
-        <v>5.5008</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>0.91</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1107</v>
+        <v>-0.1025</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.6568</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>0.78</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3528</v>
+        <v>-0.2361</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.4672</v>
+        <v>-5.6664</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4896</v>
+        <v>-0.3223</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.7504</v>
+        <v>-7.7352</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.64</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5586</v>
+        <v>-0.3695</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.4064</v>
+        <v>-8.868</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.48</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1455</v>
+        <v>1.0999</v>
       </c>
       <c r="J192" t="n">
-        <v>28.6375</v>
+        <v>27.4975</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>1.43</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0414</v>
+        <v>1.0347</v>
       </c>
       <c r="J193" t="n">
-        <v>26.035</v>
+        <v>25.8675</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6257</v>
+        <v>0.6883</v>
       </c>
       <c r="J194" t="n">
-        <v>15.6425</v>
+        <v>17.2075</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2321</v>
+        <v>0.3132</v>
       </c>
       <c r="J195" t="n">
-        <v>5.8025</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1759</v>
+        <v>0.2564</v>
       </c>
       <c r="J196" t="n">
-        <v>4.3975</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3181</v>
+        <v>0.3402</v>
       </c>
       <c r="J197" t="n">
-        <v>7.9525</v>
+        <v>8.505000000000001</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0326</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.2175</v>
+        <v>-0.8149999999999999</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>0.78</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3682</v>
+        <v>-0.2403</v>
       </c>
       <c r="J199" t="n">
-        <v>-9.205</v>
+        <v>-6.0075</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>0.73</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4433</v>
+        <v>-0.2888</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.0825</v>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>0.65</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5541</v>
+        <v>-0.3649</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.8525</v>
+        <v>-9.1225</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>1.37</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0235</v>
+        <v>0.9967</v>
       </c>
       <c r="J202" t="n">
-        <v>30.705</v>
+        <v>29.901</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6287</v>
+        <v>0.5952</v>
       </c>
       <c r="J203" t="n">
-        <v>18.861</v>
+        <v>17.856</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.524</v>
+        <v>0.4919</v>
       </c>
       <c r="J204" t="n">
-        <v>15.72</v>
+        <v>14.757</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3064</v>
+        <v>-0.2465</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.192</v>
+        <v>-7.395</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.0331</v>
+        <v>-1.0129</v>
       </c>
       <c r="J206" t="n">
-        <v>-30.993</v>
+        <v>-30.387</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.21</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4035</v>
+        <v>0.4624</v>
       </c>
       <c r="J207" t="n">
-        <v>12.105</v>
+        <v>13.872</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1809</v>
+        <v>0.1873</v>
       </c>
       <c r="J208" t="n">
-        <v>5.427</v>
+        <v>5.619</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>0.9</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2226</v>
+        <v>-0.1325</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.678</v>
+        <v>-3.975</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>0.88</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2565</v>
+        <v>-0.1543</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.695</v>
+        <v>-4.629</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>0.86</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2889</v>
+        <v>-0.1756</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.667</v>
+        <v>-5.268</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4500/event_4500_evp_summary.xlsx
+++ b/database/event/4500/event_4500_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.3249</v>
+        <v>6.5562</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5408</v>
+        <v>1.5972</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2174</v>
+        <v>2.3603</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3249</v>
+        <v>6.5562</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8731</v>
+        <v>1.9755</v>
       </c>
       <c r="H2" t="n">
-        <v>11.0583</v>
+        <v>10.5548</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7498</v>
+        <v>5.6995</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8731</v>
+        <v>1.9755</v>
       </c>
       <c r="K2" t="n">
         <v>123</v>
@@ -529,7 +529,7 @@
         <v>105</v>
       </c>
       <c r="M2" t="n">
-        <v>7.6229</v>
+        <v>7.675</v>
       </c>
       <c r="N2" t="n">
         <v>228</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.876</v>
+        <v>5.8374</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4315</v>
+        <v>1.4221</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0147</v>
+        <v>2.0331</v>
       </c>
       <c r="E3" t="n">
-        <v>5.876</v>
+        <v>5.8374</v>
       </c>
       <c r="F3" t="n">
-        <v>3.082</v>
+        <v>3.0058</v>
       </c>
       <c r="G3" t="n">
-        <v>2.794</v>
+        <v>2.8316</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3728</v>
+        <v>5.0232</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7936</v>
+        <v>2.7125</v>
       </c>
       <c r="J3" t="n">
-        <v>2.794</v>
+        <v>2.8316</v>
       </c>
       <c r="K3" t="n">
         <v>123</v>
@@ -575,7 +575,7 @@
         <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5876</v>
+        <v>5.5441</v>
       </c>
       <c r="N3" t="n">
         <v>228</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5984</v>
+        <v>5.6506</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3639</v>
+        <v>1.3766</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8894</v>
+        <v>1.9481</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5984</v>
+        <v>5.6506</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0107</v>
+        <v>2.9582</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5877</v>
+        <v>2.6924</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1214</v>
+        <v>4.866</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6629</v>
+        <v>2.6276</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5877</v>
+        <v>2.6924</v>
       </c>
       <c r="K4" t="n">
         <v>123</v>
@@ -621,7 +621,7 @@
         <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2506</v>
+        <v>5.32</v>
       </c>
       <c r="N4" t="n">
         <v>228</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4094</v>
+        <v>4.4947</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0742</v>
+        <v>1.095</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3526</v>
+        <v>1.4219</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4094</v>
+        <v>4.4947</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4422</v>
+        <v>2.3607</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9673</v>
+        <v>2.134</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1184</v>
+        <v>2.8945</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6214</v>
+        <v>1.563</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9673</v>
+        <v>2.134</v>
       </c>
       <c r="K5" t="n">
         <v>133</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5887</v>
+        <v>3.697</v>
       </c>
       <c r="N5" t="n">
         <v>234</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6642</v>
+        <v>3.6502</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8927</v>
+        <v>0.8892</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0162</v>
+        <v>1.0374</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6642</v>
+        <v>3.6502</v>
       </c>
       <c r="F6" t="n">
-        <v>2.526</v>
+        <v>2.4423</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1382</v>
+        <v>1.2079</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4138</v>
+        <v>3.1638</v>
       </c>
       <c r="I6" t="n">
-        <v>1.775</v>
+        <v>1.7084</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1382</v>
+        <v>1.2079</v>
       </c>
       <c r="K6" t="n">
         <v>133</v>
@@ -713,7 +713,7 @@
         <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9132</v>
+        <v>2.9163</v>
       </c>
       <c r="N6" t="n">
         <v>234</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.466</v>
+        <v>3.5787</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8444</v>
+        <v>0.8718</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9267</v>
+        <v>1.0049</v>
       </c>
       <c r="E7" t="n">
-        <v>3.466</v>
+        <v>3.5787</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3321</v>
+        <v>2.3007</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1339</v>
+        <v>1.278</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7306</v>
+        <v>2.6967</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4198</v>
+        <v>1.4562</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1339</v>
+        <v>1.278</v>
       </c>
       <c r="K7" t="n">
         <v>123</v>
@@ -759,7 +759,7 @@
         <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5537</v>
+        <v>2.7342</v>
       </c>
       <c r="N7" t="n">
         <v>228</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9184</v>
+        <v>2.9625</v>
       </c>
       <c r="C8" t="n">
-        <v>0.711</v>
+        <v>0.7217</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6795</v>
+        <v>0.7244</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9184</v>
+        <v>2.9625</v>
       </c>
       <c r="F8" t="n">
-        <v>2.291</v>
+        <v>2.2104</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6274</v>
+        <v>0.7521</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5858</v>
+        <v>2.3987</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3445</v>
+        <v>1.2953</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6274</v>
+        <v>0.7521</v>
       </c>
       <c r="K8" t="n">
         <v>133</v>
@@ -805,7 +805,7 @@
         <v>101</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9719</v>
+        <v>2.0474</v>
       </c>
       <c r="N8" t="n">
         <v>234</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5132</v>
+        <v>2.4018</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6123</v>
+        <v>0.5851</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4966</v>
+        <v>0.4691</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5132</v>
+        <v>2.4018</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0221</v>
+        <v>2.9421</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5089</v>
+        <v>-0.5403</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1617</v>
+        <v>4.8129</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6839</v>
+        <v>2.5989</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5089</v>
+        <v>-0.5403</v>
       </c>
       <c r="K9" t="n">
         <v>130</v>
@@ -851,7 +851,7 @@
         <v>50</v>
       </c>
       <c r="M9" t="n">
-        <v>2.175</v>
+        <v>2.0586</v>
       </c>
       <c r="N9" t="n">
         <v>180</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4103</v>
+        <v>2.3171</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5645</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4501</v>
+        <v>0.4306</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4103</v>
+        <v>2.3171</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4103</v>
+        <v>2.3171</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4103</v>
+        <v>2.3465</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4103</v>
+        <v>2.3465</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4103</v>
+        <v>2.3465</v>
       </c>
       <c r="N10" t="n">
         <v>139</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1683</v>
+        <v>2.0692</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5282</v>
+        <v>0.5041</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3409</v>
+        <v>0.3177</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1683</v>
+        <v>2.0692</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2211</v>
+        <v>1.0215</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9472</v>
+        <v>1.0477</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2211</v>
+        <v>1.0215</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6349</v>
+        <v>0.5516</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9472</v>
+        <v>1.0477</v>
       </c>
       <c r="K11" t="n">
         <v>133</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5821</v>
+        <v>1.5993</v>
       </c>
       <c r="N11" t="n">
         <v>234</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1051</v>
+        <v>1.9949</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5128</v>
+        <v>0.486</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3123</v>
+        <v>0.2839</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1051</v>
+        <v>1.9949</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6495</v>
+        <v>2.5677</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5444</v>
+        <v>-0.5728</v>
       </c>
       <c r="H12" t="n">
-        <v>3.849</v>
+        <v>3.5776</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0013</v>
+        <v>1.9319</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5444</v>
+        <v>-0.5728</v>
       </c>
       <c r="K12" t="n">
         <v>130</v>
@@ -989,7 +989,7 @@
         <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4569</v>
+        <v>1.3591</v>
       </c>
       <c r="N12" t="n">
         <v>180</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9592</v>
+        <v>1.8706</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4773</v>
+        <v>0.4557</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2465</v>
+        <v>0.2273</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9592</v>
+        <v>1.8706</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9592</v>
+        <v>1.8706</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9592</v>
+        <v>1.8706</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9592</v>
+        <v>1.8706</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9592</v>
+        <v>1.8706</v>
       </c>
       <c r="N13" t="n">
         <v>143</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7556</v>
+        <v>1.6161</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4277</v>
+        <v>0.3937</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1546</v>
+        <v>0.1115</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7556</v>
+        <v>1.6161</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7556</v>
+        <v>1.6161</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7556</v>
+        <v>1.6161</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7556</v>
+        <v>1.6161</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7556</v>
+        <v>1.6161</v>
       </c>
       <c r="N14" t="n">
         <v>143</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TenZ</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5735</v>
+        <v>1.4626</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3833</v>
+        <v>0.3563</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0723</v>
+        <v>0.0416</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5735</v>
+        <v>1.4626</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6928</v>
+        <v>0.9939</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1193</v>
+        <v>0.4687</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6928</v>
+        <v>0.9939</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8802</v>
+        <v>0.5367</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1193</v>
+        <v>0.4687</v>
       </c>
       <c r="K15" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="L15" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7609</v>
+        <v>1.0054</v>
       </c>
       <c r="N15" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>TenZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3676</v>
+        <v>1.4518</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3332</v>
+        <v>0.3537</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0206</v>
+        <v>0.0367</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3676</v>
+        <v>1.4518</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9607</v>
+        <v>1.5985</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4069</v>
+        <v>-0.1467</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9607</v>
+        <v>1.5985</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4995</v>
+        <v>0.8632</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4069</v>
+        <v>-0.1467</v>
       </c>
       <c r="K16" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="L16" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9064</v>
+        <v>0.7164999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>228</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3419</v>
+        <v>1.124</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3269</v>
+        <v>0.2738</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0322</v>
+        <v>-0.1125</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3419</v>
+        <v>1.124</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5661</v>
+        <v>1.3754</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2242</v>
+        <v>-0.2514</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5661</v>
+        <v>1.3754</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8143</v>
+        <v>0.7427</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2242</v>
+        <v>-0.2514</v>
       </c>
       <c r="K17" t="n">
         <v>140</v>
@@ -1219,7 +1219,7 @@
         <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5901000000000001</v>
+        <v>0.4913</v>
       </c>
       <c r="N17" t="n">
         <v>194</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1796</v>
+        <v>1.1086</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2874</v>
+        <v>0.2701</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1055</v>
+        <v>-0.1195</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1796</v>
+        <v>1.1086</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1796</v>
+        <v>1.1086</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1796</v>
+        <v>1.1086</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1796</v>
+        <v>1.1086</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1796</v>
+        <v>1.1086</v>
       </c>
       <c r="N18" t="n">
         <v>139</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8314</v>
+        <v>0.774</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2025</v>
+        <v>0.1886</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2627</v>
+        <v>-0.2719</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8314</v>
+        <v>0.774</v>
       </c>
       <c r="F19" t="n">
-        <v>0.882</v>
+        <v>0.8343</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0506</v>
+        <v>-0.0603</v>
       </c>
       <c r="H19" t="n">
-        <v>0.882</v>
+        <v>0.8343</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4586</v>
+        <v>0.4505</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0506</v>
+        <v>-0.0603</v>
       </c>
       <c r="K19" t="n">
         <v>140</v>
@@ -1311,7 +1311,7 @@
         <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.408</v>
+        <v>0.3902</v>
       </c>
       <c r="N19" t="n">
         <v>194</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3543</v>
+        <v>0.3172</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0863</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4781</v>
+        <v>-0.4798</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3543</v>
+        <v>0.3172</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3543</v>
+        <v>0.3172</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3543</v>
+        <v>0.3172</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3543</v>
+        <v>0.3172</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3543</v>
+        <v>0.3172</v>
       </c>
       <c r="N20" t="n">
         <v>139</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.335</v>
+        <v>0.3062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0746</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4868</v>
+        <v>-0.4848</v>
       </c>
       <c r="E21" t="n">
-        <v>0.335</v>
+        <v>0.3062</v>
       </c>
       <c r="F21" t="n">
-        <v>0.335</v>
+        <v>0.3062</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.335</v>
+        <v>0.3062</v>
       </c>
       <c r="I21" t="n">
-        <v>0.335</v>
+        <v>0.3062</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.335</v>
+        <v>0.3062</v>
       </c>
       <c r="N21" t="n">
         <v>143</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0764</v>
+        <v>-0.1076</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0186</v>
+        <v>-0.0262</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6035</v>
+        <v>-0.6732</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0764</v>
+        <v>-0.1076</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5556</v>
+        <v>0.4089</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4792</v>
+        <v>-0.5165</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5556</v>
+        <v>0.4089</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2889</v>
+        <v>0.2208</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4792</v>
+        <v>-0.5165</v>
       </c>
       <c r="K22" t="n">
         <v>130</v>
@@ -1449,7 +1449,7 @@
         <v>50</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1903</v>
+        <v>-0.2957</v>
       </c>
       <c r="N22" t="n">
         <v>180</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.119</v>
+        <v>-0.1244</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.029</v>
+        <v>-0.0303</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6917</v>
+        <v>-0.6808</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.119</v>
+        <v>-0.1244</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2091</v>
+        <v>-0.2589</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0901</v>
+        <v>0.1345</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2091</v>
+        <v>-0.2589</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1087</v>
+        <v>-0.1398</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0901</v>
+        <v>0.1345</v>
       </c>
       <c r="K23" t="n">
         <v>130</v>
@@ -1495,7 +1495,7 @@
         <v>50</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.01860000000000001</v>
+        <v>-0.005299999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>180</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1315</v>
+        <v>-0.1511</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.032</v>
+        <v>-0.0368</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6974</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1315</v>
+        <v>-0.1511</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1315</v>
+        <v>-0.1511</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1315</v>
+        <v>-0.1511</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1315</v>
+        <v>-0.1511</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1315</v>
+        <v>-0.1511</v>
       </c>
       <c r="N24" t="n">
         <v>143</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1319</v>
+        <v>-0.1879</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0321</v>
+        <v>-0.0458</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6976</v>
+        <v>-0.7097</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1319</v>
+        <v>-0.1879</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1319</v>
+        <v>-0.1879</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1319</v>
+        <v>-0.1879</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1319</v>
+        <v>-0.1879</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1319</v>
+        <v>-0.1879</v>
       </c>
       <c r="N25" t="n">
         <v>139</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9278</v>
+        <v>-0.9087</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.226</v>
+        <v>-0.2214</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.0569</v>
+        <v>-1.0379</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9278</v>
+        <v>-0.9087</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7856</v>
+        <v>-0.7613</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1422</v>
+        <v>-0.1474</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7856</v>
+        <v>-0.7613</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4085</v>
+        <v>-0.4111</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1422</v>
+        <v>-0.1474</v>
       </c>
       <c r="K26" t="n">
         <v>140</v>
@@ -1633,7 +1633,7 @@
         <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5507</v>
+        <v>-0.5585</v>
       </c>
       <c r="N26" t="n">
         <v>194</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.1954</v>
+        <v>-1.2119</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2912</v>
+        <v>-0.2952</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.1777</v>
+        <v>-1.1759</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.1954</v>
+        <v>-1.2119</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.1747</v>
+        <v>-1.1802</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0207</v>
+        <v>-0.0317</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.1747</v>
+        <v>-1.1802</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6108</v>
+        <v>-0.6373</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0207</v>
+        <v>-0.0317</v>
       </c>
       <c r="K27" t="n">
         <v>140</v>
@@ -1679,7 +1679,7 @@
         <v>54</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6315000000000001</v>
+        <v>-0.6689999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>194</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.2093</v>
+        <v>-1.2312</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2946</v>
+        <v>-0.2999</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.184</v>
+        <v>-1.1847</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.2093</v>
+        <v>-1.2312</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.2093</v>
+        <v>-1.2312</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.2093</v>
+        <v>-1.2312</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.2093</v>
+        <v>-1.2312</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.2093</v>
+        <v>-1.2312</v>
       </c>
       <c r="N28" t="n">
         <v>139</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.346</v>
+        <v>-1.281</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3279</v>
+        <v>-0.3121</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2457</v>
+        <v>-1.2073</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.346</v>
+        <v>-1.281</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9845</v>
+        <v>-0.8802</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3615</v>
+        <v>-0.4008</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9845</v>
+        <v>-0.8802</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5119</v>
+        <v>-0.4753</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3615</v>
+        <v>-0.4008</v>
       </c>
       <c r="K29" t="n">
         <v>130</v>
@@ -1771,7 +1771,7 @@
         <v>50</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.8734</v>
+        <v>-0.8761</v>
       </c>
       <c r="N29" t="n">
         <v>180</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.0463</v>
+        <v>-2.005</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4985</v>
+        <v>-0.4884</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.5618</v>
+        <v>-1.5369</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.0463</v>
+        <v>-2.005</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.0463</v>
+        <v>-2.005</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.0463</v>
+        <v>-2.005</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.0463</v>
+        <v>-2.005</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.0463</v>
+        <v>-2.005</v>
       </c>
       <c r="N30" t="n">
         <v>143</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.7329</v>
+        <v>-2.5921</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.6315</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.8718</v>
+        <v>-1.8042</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.7329</v>
+        <v>-2.5921</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.1742</v>
+        <v>-2.0497</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5587</v>
+        <v>-0.5424</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.1742</v>
+        <v>-2.0497</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.1305</v>
+        <v>-1.1068</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5587</v>
+        <v>-0.5424</v>
       </c>
       <c r="K31" t="n">
         <v>133</v>
@@ -1863,7 +1863,7 @@
         <v>101</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.6892</v>
+        <v>-1.6492</v>
       </c>
       <c r="N31" t="n">
         <v>234</v>
@@ -1969,10 +1969,10 @@
         <v>1.44</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0754</v>
+        <v>1.0405</v>
       </c>
       <c r="J2" t="n">
-        <v>31.1866</v>
+        <v>30.1745</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7611</v>
+        <v>0.7218</v>
       </c>
       <c r="J3" t="n">
-        <v>22.0719</v>
+        <v>20.9322</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3135</v>
+        <v>0.3178</v>
       </c>
       <c r="J4" t="n">
-        <v>9.0915</v>
+        <v>9.216200000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0185</v>
+        <v>0.0347</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5365</v>
+        <v>1.0063</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.93</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3016</v>
+        <v>-0.2885</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.7464</v>
+        <v>-8.3665</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4453</v>
+        <v>0.4386</v>
       </c>
       <c r="J7" t="n">
-        <v>12.9137</v>
+        <v>12.7194</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3701</v>
+        <v>0.3686</v>
       </c>
       <c r="J8" t="n">
-        <v>10.7329</v>
+        <v>10.6894</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.93</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.098</v>
+        <v>-0.1099</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.842</v>
+        <v>-3.1871</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1856</v>
+        <v>-0.1997</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.3824</v>
+        <v>-5.7913</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2762</v>
+        <v>-0.2896</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.0098</v>
+        <v>-8.398400000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>2.18</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J12" t="n">
-        <v>41.0982</v>
+        <v>40.5966</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.38</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.877</v>
       </c>
       <c r="J13" t="n">
-        <v>20.3258</v>
+        <v>19.294</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7493</v>
+        <v>0.7227</v>
       </c>
       <c r="J14" t="n">
-        <v>16.4846</v>
+        <v>15.8994</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.24</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6099</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>13.4178</v>
+        <v>13.1846</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>1.07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1614</v>
+        <v>0.1913</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5508</v>
+        <v>4.2086</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>0.89</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1179</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.0504</v>
+        <v>-2.5938</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1843</v>
+        <v>-0.2079</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.0546</v>
+        <v>-4.5738</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3304</v>
+        <v>-0.3502</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.2688</v>
+        <v>-7.7044</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.61</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3763</v>
+        <v>-0.3941</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.278600000000001</v>
+        <v>-8.670199999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.42</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5542</v>
+        <v>-0.5611</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.1924</v>
+        <v>-12.3442</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.61</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9571</v>
+        <v>1.0616</v>
       </c>
       <c r="J22" t="n">
-        <v>22.0133</v>
+        <v>24.4168</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.58</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9216</v>
+        <v>1.0236</v>
       </c>
       <c r="J23" t="n">
-        <v>21.1968</v>
+        <v>23.5428</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.44</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7548</v>
+        <v>0.8427</v>
       </c>
       <c r="J24" t="n">
-        <v>17.3604</v>
+        <v>19.3821</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.4</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7071</v>
+        <v>0.7902</v>
       </c>
       <c r="J25" t="n">
-        <v>16.2633</v>
+        <v>18.1746</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.13</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3297</v>
+        <v>0.3497</v>
       </c>
       <c r="J26" t="n">
-        <v>7.5831</v>
+        <v>8.043100000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1127</v>
+        <v>-0.1382</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.5921</v>
+        <v>-3.1786</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1914</v>
+        <v>-0.2156</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.4022</v>
+        <v>-4.9588</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.59</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3925</v>
+        <v>-0.41</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.0275</v>
+        <v>-9.43</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.54</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4392</v>
+        <v>-0.4541</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.1016</v>
+        <v>-10.4443</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4579</v>
+        <v>-0.4717</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.5317</v>
+        <v>-10.8491</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.72</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1441</v>
+        <v>1.2505</v>
       </c>
       <c r="J32" t="n">
-        <v>30.8907</v>
+        <v>33.7635</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4101</v>
+        <v>0.4513</v>
       </c>
       <c r="J33" t="n">
-        <v>11.0727</v>
+        <v>12.1851</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.395</v>
+        <v>0.4316</v>
       </c>
       <c r="J34" t="n">
-        <v>10.665</v>
+        <v>11.6532</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.08</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2453</v>
+        <v>0.257</v>
       </c>
       <c r="J35" t="n">
-        <v>6.6231</v>
+        <v>6.939</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.46</v>
+        <v>-0.432</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.42</v>
+        <v>-11.664</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.33</v>
       </c>
       <c r="I37" t="n">
-        <v>0.548</v>
+        <v>0.6062</v>
       </c>
       <c r="J37" t="n">
-        <v>14.796</v>
+        <v>16.3674</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.92</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1052</v>
+        <v>-0.1187</v>
       </c>
       <c r="J38" t="n">
-        <v>-2.8404</v>
+        <v>-3.2049</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.91</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1164</v>
+        <v>-0.1303</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.1428</v>
+        <v>-3.5181</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.86</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1701</v>
+        <v>-0.1852</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.5927</v>
+        <v>-5.0004</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.66</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3665</v>
+        <v>-0.3783</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.8955</v>
+        <v>-10.2141</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.75</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1431</v>
+        <v>1.2557</v>
       </c>
       <c r="J42" t="n">
-        <v>27.4344</v>
+        <v>30.1368</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.68</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0597</v>
+        <v>1.1674</v>
       </c>
       <c r="J43" t="n">
-        <v>25.4328</v>
+        <v>28.0176</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3003</v>
+        <v>0.3151</v>
       </c>
       <c r="J44" t="n">
-        <v>7.2072</v>
+        <v>7.5624</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1841</v>
+        <v>0.2072</v>
       </c>
       <c r="J45" t="n">
-        <v>4.4184</v>
+        <v>4.9728</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0882</v>
+        <v>0.1161</v>
       </c>
       <c r="J46" t="n">
-        <v>2.1168</v>
+        <v>2.7864</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>0.96</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0255</v>
+        <v>-0.0433</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.612</v>
+        <v>-1.0392</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>0.84</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1689</v>
+        <v>-0.1892</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.0536</v>
+        <v>-4.5408</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.72</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2853</v>
+        <v>-0.3043</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.8472</v>
+        <v>-7.3032</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2946</v>
+        <v>-0.3134</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.0704</v>
+        <v>-7.5216</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4539</v>
+        <v>-0.4656</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.8936</v>
+        <v>-11.1744</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.52</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.0195</v>
       </c>
       <c r="J52" t="n">
-        <v>27.99</v>
+        <v>30.585</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7852</v>
+        <v>0.8612</v>
       </c>
       <c r="J53" t="n">
-        <v>23.556</v>
+        <v>25.836</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.9</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3683</v>
+        <v>-0.3555</v>
       </c>
       <c r="J54" t="n">
-        <v>-11.049</v>
+        <v>-10.665</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.8</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.641</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>-19.23</v>
+        <v>-18.039</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8682</v>
+        <v>-0.8011</v>
       </c>
       <c r="J56" t="n">
-        <v>-26.046</v>
+        <v>-24.033</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3117</v>
+        <v>0.3182</v>
       </c>
       <c r="J57" t="n">
-        <v>9.351000000000001</v>
+        <v>9.545999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.12</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2739</v>
+        <v>0.2817</v>
       </c>
       <c r="J58" t="n">
-        <v>8.217000000000001</v>
+        <v>8.451000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2347</v>
+        <v>0.244</v>
       </c>
       <c r="J59" t="n">
-        <v>7.041</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0553</v>
+        <v>-0.0622</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.659</v>
+        <v>-1.866</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1034</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.814</v>
+        <v>-3.102</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6952</v>
+        <v>0.6694</v>
       </c>
       <c r="J62" t="n">
-        <v>20.856</v>
+        <v>20.082</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.02</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0636</v>
+        <v>0.0717</v>
       </c>
       <c r="J63" t="n">
-        <v>1.908</v>
+        <v>2.151</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0519</v>
+        <v>-0.0596</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.557</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1252</v>
+        <v>-0.1371</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.756</v>
+        <v>-4.113</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1902</v>
+        <v>-0.2033</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.706</v>
+        <v>-6.099</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.27</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7559</v>
+        <v>0.7138</v>
       </c>
       <c r="J67" t="n">
-        <v>22.677</v>
+        <v>21.414</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5332</v>
+        <v>0.5161</v>
       </c>
       <c r="J68" t="n">
-        <v>15.996</v>
+        <v>15.483</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4298</v>
+        <v>0.4226</v>
       </c>
       <c r="J69" t="n">
-        <v>12.894</v>
+        <v>12.678</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2961</v>
+        <v>0.299</v>
       </c>
       <c r="J70" t="n">
-        <v>8.882999999999999</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6232</v>
+        <v>-0.584</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.696</v>
+        <v>-17.52</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6615</v>
+        <v>0.6446</v>
       </c>
       <c r="J72" t="n">
-        <v>19.845</v>
+        <v>19.338</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.13</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2819</v>
+        <v>0.2921</v>
       </c>
       <c r="J73" t="n">
-        <v>8.457000000000001</v>
+        <v>8.763</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1214</v>
+        <v>0.1352</v>
       </c>
       <c r="J74" t="n">
-        <v>3.642</v>
+        <v>4.056</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1214</v>
+        <v>0.1352</v>
       </c>
       <c r="J75" t="n">
-        <v>3.642</v>
+        <v>4.056</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.02</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0477</v>
+        <v>0.0603</v>
       </c>
       <c r="J76" t="n">
-        <v>1.431</v>
+        <v>1.809</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.25</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5243</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>15.729</v>
+        <v>15.408</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.11</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2631</v>
+        <v>0.2693</v>
       </c>
       <c r="J78" t="n">
-        <v>7.893</v>
+        <v>8.079000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1366</v>
+        <v>0.146</v>
       </c>
       <c r="J79" t="n">
-        <v>4.098</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1015</v>
+        <v>-0.1127</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.045</v>
+        <v>-3.381</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3092</v>
+        <v>-0.3211</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.276</v>
+        <v>-9.632999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6155</v>
+        <v>0.5883</v>
       </c>
       <c r="J82" t="n">
-        <v>16.6185</v>
+        <v>15.8841</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.17</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5135</v>
+        <v>0.4972</v>
       </c>
       <c r="J83" t="n">
-        <v>13.8645</v>
+        <v>13.4244</v>
       </c>
     </row>
     <row r="84">
@@ -5289,10 +5289,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2126</v>
+        <v>0.2193</v>
       </c>
       <c r="J85" t="n">
-        <v>5.7402</v>
+        <v>5.9211</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5111</v>
+        <v>-0.4847</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.7997</v>
+        <v>-13.0869</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6027</v>
+        <v>0.5868</v>
       </c>
       <c r="J87" t="n">
-        <v>16.2729</v>
+        <v>15.8436</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2769</v>
+        <v>0.2839</v>
       </c>
       <c r="J88" t="n">
-        <v>7.4763</v>
+        <v>7.6653</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0539</v>
+        <v>-0.0611</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.4553</v>
+        <v>-1.6497</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.08</v>
+        <v>-0.0892</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.16</v>
+        <v>-2.4084</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.182</v>
+        <v>-0.1944</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.914</v>
+        <v>-5.2488</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.29</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6301</v>
+        <v>0.6039</v>
       </c>
       <c r="J92" t="n">
-        <v>16.3826</v>
+        <v>15.7014</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2881</v>
+        <v>0.2876</v>
       </c>
       <c r="J93" t="n">
-        <v>7.4906</v>
+        <v>7.4776</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.83</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2001</v>
+        <v>-0.2156</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.2026</v>
+        <v>-5.6056</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2502</v>
+        <v>-0.2653</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.5052</v>
+        <v>-6.8978</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.63</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3936</v>
+        <v>-0.4044</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.2336</v>
+        <v>-10.5144</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1139</v>
+        <v>1.0723</v>
       </c>
       <c r="J97" t="n">
-        <v>28.9614</v>
+        <v>27.8798</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7834</v>
+        <v>0.7416</v>
       </c>
       <c r="J98" t="n">
-        <v>20.3684</v>
+        <v>19.2816</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.17</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4942</v>
+        <v>0.4839</v>
       </c>
       <c r="J99" t="n">
-        <v>12.8492</v>
+        <v>12.5814</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0955</v>
+        <v>0.1118</v>
       </c>
       <c r="J100" t="n">
-        <v>2.483</v>
+        <v>2.9068</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.82</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6122</v>
+        <v>-0.5713</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.9172</v>
+        <v>-14.8538</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2371</v>
+        <v>-0.2651</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.742</v>
+        <v>-5.302</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.7</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2692</v>
+        <v>-0.2956</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.384</v>
+        <v>-5.912</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.57</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3957</v>
+        <v>-0.4158</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.914</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.48</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4774</v>
+        <v>-0.4927</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.548</v>
+        <v>-9.853999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.36</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5926</v>
+        <v>-0.5991</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.852</v>
+        <v>-11.982</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.93</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5948</v>
+        <v>1.5952</v>
       </c>
       <c r="J107" t="n">
-        <v>31.896</v>
+        <v>31.904</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1802</v>
+        <v>1.1553</v>
       </c>
       <c r="J108" t="n">
-        <v>23.604</v>
+        <v>23.106</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9772</v>
+        <v>0.9291</v>
       </c>
       <c r="J109" t="n">
-        <v>19.544</v>
+        <v>18.582</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.27</v>
       </c>
       <c r="I110" t="n">
-        <v>0.676</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>13.52</v>
+        <v>13.176</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2448</v>
+        <v>0.27</v>
       </c>
       <c r="J111" t="n">
-        <v>4.896</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.26</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5386</v>
+        <v>0.5273</v>
       </c>
       <c r="J112" t="n">
-        <v>15.0808</v>
+        <v>14.7644</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.21</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4495</v>
+        <v>0.4452</v>
       </c>
       <c r="J113" t="n">
-        <v>12.586</v>
+        <v>12.4656</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0906</v>
+        <v>-0.1009</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.5368</v>
+        <v>-2.8252</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.87</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1696</v>
+        <v>-0.1823</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.7488</v>
+        <v>-5.1044</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2011</v>
+        <v>-0.2141</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.6308</v>
+        <v>-5.9948</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8501</v>
+        <v>0.7965</v>
       </c>
       <c r="J117" t="n">
-        <v>23.8028</v>
+        <v>22.302</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.22</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6323</v>
+        <v>0.6049</v>
       </c>
       <c r="J118" t="n">
-        <v>17.7044</v>
+        <v>16.9372</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4026</v>
+        <v>0.3979</v>
       </c>
       <c r="J119" t="n">
-        <v>11.2728</v>
+        <v>11.1412</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>0.109</v>
+        <v>0.1212</v>
       </c>
       <c r="J120" t="n">
-        <v>3.052</v>
+        <v>3.3936</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.598</v>
+        <v>-0.5613</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.744</v>
+        <v>-15.7164</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.15</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3788</v>
+        <v>0.3709</v>
       </c>
       <c r="J122" t="n">
-        <v>10.2276</v>
+        <v>10.0143</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.05</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1653</v>
+        <v>0.1667</v>
       </c>
       <c r="J123" t="n">
-        <v>4.4631</v>
+        <v>4.5009</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2171</v>
+        <v>-0.2332</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.8617</v>
+        <v>-6.2964</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.77</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2568</v>
+        <v>-0.2724</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.9336</v>
+        <v>-7.3548</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2957</v>
+        <v>-0.3105</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.9839</v>
+        <v>-8.3835</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.71</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4225</v>
+        <v>1.3999</v>
       </c>
       <c r="J127" t="n">
-        <v>38.4075</v>
+        <v>37.7973</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.13</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3953</v>
+        <v>0.393</v>
       </c>
       <c r="J128" t="n">
-        <v>10.6731</v>
+        <v>10.611</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1651</v>
+        <v>0.1784</v>
       </c>
       <c r="J129" t="n">
-        <v>4.4577</v>
+        <v>4.8168</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0975</v>
+        <v>0.1132</v>
       </c>
       <c r="J130" t="n">
-        <v>2.6325</v>
+        <v>3.0564</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6101</v>
+        <v>-0.5699</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.4727</v>
+        <v>-15.3873</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.17</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3866</v>
+        <v>0.3845</v>
       </c>
       <c r="J132" t="n">
-        <v>10.8248</v>
+        <v>10.766</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2078</v>
+        <v>0.2145</v>
       </c>
       <c r="J133" t="n">
-        <v>5.8184</v>
+        <v>6.006</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1864</v>
+        <v>0.1936</v>
       </c>
       <c r="J134" t="n">
-        <v>5.2192</v>
+        <v>5.4208</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1866</v>
+        <v>-0.2004</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.2248</v>
+        <v>-5.6112</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2674</v>
+        <v>-0.2807</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.4872</v>
+        <v>-7.8596</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.27</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8004</v>
+        <v>0.745</v>
       </c>
       <c r="J137" t="n">
-        <v>22.4112</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.094</v>
+        <v>0.0997</v>
       </c>
       <c r="J138" t="n">
-        <v>2.632</v>
+        <v>2.7916</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.053</v>
+        <v>-0.0585</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.484</v>
+        <v>-1.638</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2896</v>
+        <v>-0.2873</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.1088</v>
+        <v>-8.0444</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6465</v>
+        <v>-0.61</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.102</v>
+        <v>-17.08</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.69</v>
       </c>
       <c r="I142" t="n">
-        <v>1.379</v>
+        <v>1.3572</v>
       </c>
       <c r="J142" t="n">
-        <v>33.096</v>
+        <v>32.5728</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5117</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J143" t="n">
-        <v>12.2808</v>
+        <v>12.036</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.08</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2439</v>
+        <v>0.256</v>
       </c>
       <c r="J144" t="n">
-        <v>5.8536</v>
+        <v>6.144</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2139</v>
+        <v>0.228</v>
       </c>
       <c r="J145" t="n">
-        <v>5.1336</v>
+        <v>5.472</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0496</v>
+        <v>-0.0343</v>
       </c>
       <c r="J146" t="n">
-        <v>-1.1904</v>
+        <v>-0.8232</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.24</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5511</v>
+        <v>0.5301</v>
       </c>
       <c r="J147" t="n">
-        <v>13.2264</v>
+        <v>12.7224</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.89</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1349</v>
+        <v>-0.1503</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.2376</v>
+        <v>-3.6072</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.87</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1559</v>
+        <v>-0.1717</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.7416</v>
+        <v>-4.1208</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.84</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1868</v>
+        <v>-0.2029</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.4832</v>
+        <v>-4.8696</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.67</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3529</v>
+        <v>-0.3659</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.4696</v>
+        <v>-8.781599999999999</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.43</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8205</v>
+        <v>0.7832</v>
       </c>
       <c r="J152" t="n">
-        <v>24.615</v>
+        <v>23.496</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.15</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3344</v>
+        <v>0.3385</v>
       </c>
       <c r="J153" t="n">
-        <v>10.032</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1967</v>
+        <v>0.2065</v>
       </c>
       <c r="J154" t="n">
-        <v>5.901</v>
+        <v>6.195</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2132</v>
+        <v>-0.2258</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.396</v>
+        <v>-6.774</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3311</v>
+        <v>-0.3419</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.933</v>
+        <v>-10.257</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.14</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3297</v>
+        <v>0.331</v>
       </c>
       <c r="J157" t="n">
-        <v>9.891</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3102</v>
+        <v>0.3125</v>
       </c>
       <c r="J158" t="n">
-        <v>9.305999999999999</v>
+        <v>9.375</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0684</v>
+        <v>0.0751</v>
       </c>
       <c r="J159" t="n">
-        <v>2.052</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.86</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1758</v>
+        <v>-0.1897</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.274</v>
+        <v>-5.691</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.78</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2573</v>
+        <v>-0.2708</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.719</v>
+        <v>-8.124000000000001</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8449</v>
+        <v>0.797</v>
       </c>
       <c r="J162" t="n">
-        <v>21.1225</v>
+        <v>19.925</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6581</v>
+        <v>0.6323</v>
       </c>
       <c r="J163" t="n">
-        <v>16.4525</v>
+        <v>15.8075</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.19</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5387</v>
+        <v>0.5253</v>
       </c>
       <c r="J164" t="n">
-        <v>13.4675</v>
+        <v>13.1325</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.1</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3067</v>
+        <v>0.3131</v>
       </c>
       <c r="J165" t="n">
-        <v>7.6675</v>
+        <v>7.8275</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1885</v>
+        <v>0.2027</v>
       </c>
       <c r="J166" t="n">
-        <v>4.7125</v>
+        <v>5.0675</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.48</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9254</v>
+        <v>0.8739</v>
       </c>
       <c r="J167" t="n">
-        <v>23.135</v>
+        <v>21.8475</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.1725</v>
+        <v>-2.4525</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.92</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1104</v>
+        <v>-0.1226</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.76</v>
+        <v>-3.065</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2276</v>
+        <v>-0.2414</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.69</v>
+        <v>-6.035</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2476</v>
+        <v>-0.2612</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.19</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.5</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1689</v>
+        <v>1.1285</v>
       </c>
       <c r="J172" t="n">
-        <v>35.067</v>
+        <v>33.855</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.05</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1762</v>
+        <v>0.186</v>
       </c>
       <c r="J173" t="n">
-        <v>5.286</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.109</v>
+        <v>0.1212</v>
       </c>
       <c r="J174" t="n">
-        <v>3.27</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.97</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1565</v>
+        <v>-0.1537</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.695</v>
+        <v>-4.611</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1914</v>
+        <v>-0.1875</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.742</v>
+        <v>-5.625</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9646</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>28.938</v>
+        <v>27.384</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3829</v>
+        <v>0.3818</v>
       </c>
       <c r="J178" t="n">
-        <v>11.487</v>
+        <v>11.454</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1618</v>
+        <v>0.1701</v>
       </c>
       <c r="J179" t="n">
-        <v>4.854</v>
+        <v>5.103</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.91</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.123</v>
+        <v>-0.1354</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.69</v>
+        <v>-4.062</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.35</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6509</v>
+        <v>-0.6465</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.527</v>
+        <v>-19.395</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.81</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4947</v>
+        <v>1.4838</v>
       </c>
       <c r="J182" t="n">
-        <v>35.8728</v>
+        <v>35.6112</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.33</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="J183" t="n">
-        <v>20.0928</v>
+        <v>19.104</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6832</v>
+        <v>0.6592</v>
       </c>
       <c r="J184" t="n">
-        <v>16.3968</v>
+        <v>15.8208</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2495</v>
+        <v>0.2667</v>
       </c>
       <c r="J185" t="n">
-        <v>5.988</v>
+        <v>6.4008</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0594</v>
+        <v>0.0866</v>
       </c>
       <c r="J186" t="n">
-        <v>1.4256</v>
+        <v>2.0784</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.06</v>
       </c>
       <c r="I187" t="n">
-        <v>0.223</v>
+        <v>0.2149</v>
       </c>
       <c r="J187" t="n">
-        <v>5.352</v>
+        <v>5.1576</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>0.91</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1025</v>
+        <v>-0.1197</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.46</v>
+        <v>-2.8728</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>0.78</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2361</v>
+        <v>-0.2544</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.6664</v>
+        <v>-6.1056</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3223</v>
+        <v>-0.3385</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.7352</v>
+        <v>-8.124000000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.64</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3695</v>
+        <v>-0.3839</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.868</v>
+        <v>-9.2136</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.48</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0999</v>
+        <v>1.0622</v>
       </c>
       <c r="J192" t="n">
-        <v>27.4975</v>
+        <v>26.555</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>1.43</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0347</v>
+        <v>0.9859</v>
       </c>
       <c r="J193" t="n">
-        <v>25.8675</v>
+        <v>24.6475</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6883</v>
+        <v>0.6626</v>
       </c>
       <c r="J194" t="n">
-        <v>17.2075</v>
+        <v>16.565</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3132</v>
+        <v>0.324</v>
       </c>
       <c r="J195" t="n">
-        <v>7.83</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2564</v>
+        <v>0.2716</v>
       </c>
       <c r="J196" t="n">
-        <v>6.41</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3402</v>
+        <v>0.3302</v>
       </c>
       <c r="J197" t="n">
-        <v>8.505000000000001</v>
+        <v>8.255000000000001</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0326</v>
+        <v>-0.0448</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>0.78</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2403</v>
+        <v>-0.2576</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.0075</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>0.73</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2888</v>
+        <v>-0.3051</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.22</v>
+        <v>-7.6275</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>0.65</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3649</v>
+        <v>-0.3786</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.1225</v>
+        <v>-9.465</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>1.37</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9967</v>
+        <v>0.9306</v>
       </c>
       <c r="J202" t="n">
-        <v>29.901</v>
+        <v>27.918</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5952</v>
+        <v>0.5693</v>
       </c>
       <c r="J203" t="n">
-        <v>17.856</v>
+        <v>17.079</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4919</v>
+        <v>0.4768</v>
       </c>
       <c r="J204" t="n">
-        <v>14.757</v>
+        <v>14.304</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2465</v>
+        <v>-0.2425</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.395</v>
+        <v>-7.275</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.0129</v>
+        <v>-0.9267</v>
       </c>
       <c r="J206" t="n">
-        <v>-30.387</v>
+        <v>-27.801</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.21</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4624</v>
+        <v>0.4546</v>
       </c>
       <c r="J207" t="n">
-        <v>13.872</v>
+        <v>13.638</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1873</v>
+        <v>0.1943</v>
       </c>
       <c r="J208" t="n">
-        <v>5.619</v>
+        <v>5.829</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>0.9</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1325</v>
+        <v>-0.1456</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.975</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>0.88</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1543</v>
+        <v>-0.1679</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.629</v>
+        <v>-5.037</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>0.86</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1756</v>
+        <v>-0.1895</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.268</v>
+        <v>-5.685</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4500/event_4500_evp_summary.xlsx
+++ b/database/event/4500/event_4500_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5562</v>
+        <v>6.3906</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5972</v>
+        <v>1.5569</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3603</v>
+        <v>2.3054</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5562</v>
+        <v>6.3906</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5807</v>
+        <v>4.433</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9755</v>
+        <v>1.9576</v>
       </c>
       <c r="H2" t="n">
-        <v>10.5548</v>
+        <v>10.2009</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6995</v>
+        <v>5.7275</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9755</v>
+        <v>1.9576</v>
       </c>
       <c r="K2" t="n">
         <v>123</v>
@@ -529,7 +529,7 @@
         <v>105</v>
       </c>
       <c r="M2" t="n">
-        <v>7.675</v>
+        <v>7.6851</v>
       </c>
       <c r="N2" t="n">
         <v>228</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8374</v>
+        <v>5.7519</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4221</v>
+        <v>1.4013</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0331</v>
+        <v>2.0145</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8374</v>
+        <v>5.7519</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0058</v>
+        <v>2.9154</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8316</v>
+        <v>2.8365</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0232</v>
+        <v>4.5032</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7125</v>
+        <v>2.5284</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8316</v>
+        <v>2.8365</v>
       </c>
       <c r="K3" t="n">
         <v>123</v>
@@ -575,7 +575,7 @@
         <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5441</v>
+        <v>5.3649</v>
       </c>
       <c r="N3" t="n">
         <v>228</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6506</v>
+        <v>5.7045</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3766</v>
+        <v>1.3897</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9481</v>
+        <v>1.9929</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6506</v>
+        <v>5.7045</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9582</v>
+        <v>2.9393</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6924</v>
+        <v>2.7652</v>
       </c>
       <c r="H4" t="n">
-        <v>4.866</v>
+        <v>4.5928</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6276</v>
+        <v>2.5787</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6924</v>
+        <v>2.7652</v>
       </c>
       <c r="K4" t="n">
         <v>123</v>
@@ -621,7 +621,7 @@
         <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>5.32</v>
+        <v>5.3439</v>
       </c>
       <c r="N4" t="n">
         <v>228</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4947</v>
+        <v>4.4941</v>
       </c>
       <c r="C5" t="n">
-        <v>1.095</v>
+        <v>1.0948</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4219</v>
+        <v>1.4415</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4947</v>
+        <v>4.4941</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3607</v>
+        <v>2.4114</v>
       </c>
       <c r="G5" t="n">
-        <v>2.134</v>
+        <v>2.0827</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8945</v>
+        <v>2.611</v>
       </c>
       <c r="I5" t="n">
-        <v>1.563</v>
+        <v>1.466</v>
       </c>
       <c r="J5" t="n">
-        <v>2.134</v>
+        <v>2.0827</v>
       </c>
       <c r="K5" t="n">
         <v>133</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>3.697</v>
+        <v>3.5487</v>
       </c>
       <c r="N5" t="n">
         <v>234</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6502</v>
+        <v>3.6206</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8892</v>
+        <v>0.882</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0374</v>
+        <v>1.0436</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6502</v>
+        <v>3.6206</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4423</v>
+        <v>2.3427</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2079</v>
+        <v>1.2779</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1638</v>
+        <v>2.3529</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7084</v>
+        <v>1.3211</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2079</v>
+        <v>1.2779</v>
       </c>
       <c r="K6" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="L6" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9163</v>
+        <v>2.599</v>
       </c>
       <c r="N6" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5787</v>
+        <v>3.6072</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8718</v>
+        <v>0.8788</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0049</v>
+        <v>1.0375</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5787</v>
+        <v>3.6072</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3007</v>
+        <v>2.4787</v>
       </c>
       <c r="G7" t="n">
-        <v>1.278</v>
+        <v>1.1285</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6967</v>
+        <v>2.8636</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4562</v>
+        <v>1.6078</v>
       </c>
       <c r="J7" t="n">
-        <v>1.278</v>
+        <v>1.1285</v>
       </c>
       <c r="K7" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L7" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7342</v>
+        <v>2.7363</v>
       </c>
       <c r="N7" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9625</v>
+        <v>2.7982</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7217</v>
+        <v>0.6817</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7244</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9625</v>
+        <v>2.7982</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2104</v>
+        <v>2.069</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7521</v>
+        <v>0.7292</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3987</v>
+        <v>2.069</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2953</v>
+        <v>1.1617</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7521</v>
+        <v>0.7292</v>
       </c>
       <c r="K8" t="n">
         <v>133</v>
@@ -805,7 +805,7 @@
         <v>101</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0474</v>
+        <v>1.8909</v>
       </c>
       <c r="N8" t="n">
         <v>234</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4018</v>
+        <v>2.3967</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5851</v>
+        <v>0.5839</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4691</v>
+        <v>0.486</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4018</v>
+        <v>2.3967</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9421</v>
+        <v>2.9095</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5403</v>
+        <v>-0.5128</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8129</v>
+        <v>4.4809</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5989</v>
+        <v>2.5159</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5403</v>
+        <v>-0.5128</v>
       </c>
       <c r="K9" t="n">
         <v>130</v>
@@ -851,7 +851,7 @@
         <v>50</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0586</v>
+        <v>2.0031</v>
       </c>
       <c r="N9" t="n">
         <v>180</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3171</v>
+        <v>2.0878</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5645</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4306</v>
+        <v>0.3453</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3171</v>
+        <v>2.0878</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3171</v>
+        <v>2.0878</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3465</v>
+        <v>2.0878</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3465</v>
+        <v>2.0878</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3465</v>
+        <v>2.0878</v>
       </c>
       <c r="N10" t="n">
         <v>139</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0692</v>
+        <v>2.0725</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5041</v>
+        <v>0.5049</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3177</v>
+        <v>0.3383</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0692</v>
+        <v>2.0725</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0215</v>
+        <v>1.0309</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0477</v>
+        <v>1.0416</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0215</v>
+        <v>1.0309</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5516</v>
+        <v>0.5788</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0477</v>
+        <v>1.0416</v>
       </c>
       <c r="K11" t="n">
         <v>133</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5993</v>
+        <v>1.6204</v>
       </c>
       <c r="N11" t="n">
         <v>234</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9949</v>
+        <v>2.0345</v>
       </c>
       <c r="C12" t="n">
-        <v>0.486</v>
+        <v>0.4956</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2839</v>
+        <v>0.321</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9949</v>
+        <v>2.0345</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5677</v>
+        <v>2.5837</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5728</v>
+        <v>-0.5492</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5776</v>
+        <v>3.2575</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9319</v>
+        <v>1.829</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5728</v>
+        <v>-0.5492</v>
       </c>
       <c r="K12" t="n">
         <v>130</v>
@@ -989,7 +989,7 @@
         <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3591</v>
+        <v>1.2798</v>
       </c>
       <c r="N12" t="n">
         <v>180</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8706</v>
+        <v>1.672</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4557</v>
+        <v>0.4073</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2273</v>
+        <v>0.1559</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8706</v>
+        <v>1.672</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8706</v>
+        <v>1.672</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8706</v>
+        <v>1.672</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8706</v>
+        <v>1.672</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8706</v>
+        <v>1.672</v>
       </c>
       <c r="N13" t="n">
         <v>143</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6161</v>
+        <v>1.5273</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3937</v>
+        <v>0.3721</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1115</v>
+        <v>0.09</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6161</v>
+        <v>1.5273</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6161</v>
+        <v>1.5273</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6161</v>
+        <v>1.5273</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6161</v>
+        <v>1.5273</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6161</v>
+        <v>1.5273</v>
       </c>
       <c r="N14" t="n">
         <v>143</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4626</v>
+        <v>1.356</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3563</v>
+        <v>0.3303</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0416</v>
+        <v>0.0119</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4626</v>
+        <v>1.356</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9939</v>
+        <v>0.9418</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4687</v>
+        <v>0.4142</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9939</v>
+        <v>0.9418</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5367</v>
+        <v>0.5288</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4687</v>
+        <v>0.4142</v>
       </c>
       <c r="K15" t="n">
         <v>123</v>
@@ -1127,7 +1127,7 @@
         <v>105</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0054</v>
+        <v>0.9430000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>228</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4518</v>
+        <v>1.1542</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3537</v>
+        <v>0.2812</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0367</v>
+        <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4518</v>
+        <v>1.1542</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5985</v>
+        <v>1.2717</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1467</v>
+        <v>-0.1175</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5985</v>
+        <v>1.2717</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8632</v>
+        <v>0.714</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1467</v>
+        <v>-0.1175</v>
       </c>
       <c r="K16" t="n">
         <v>140</v>
@@ -1173,7 +1173,7 @@
         <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7164999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="N16" t="n">
         <v>194</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.124</v>
+        <v>1.0154</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2738</v>
+        <v>0.2474</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1125</v>
+        <v>-0.1432</v>
       </c>
       <c r="E17" t="n">
-        <v>1.124</v>
+        <v>1.0154</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3754</v>
+        <v>1.0154</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2514</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3754</v>
+        <v>1.0154</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7427</v>
+        <v>1.0154</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2514</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4913</v>
+        <v>1.0154</v>
       </c>
       <c r="N17" t="n">
-        <v>194</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1086</v>
+        <v>0.9716</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2701</v>
+        <v>0.2367</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1195</v>
+        <v>-0.1632</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1086</v>
+        <v>0.9716</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1086</v>
+        <v>1.1937</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.2221</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1086</v>
+        <v>1.1937</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1086</v>
+        <v>0.6702</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.2221</v>
       </c>
       <c r="K18" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1086</v>
+        <v>0.4481000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>139</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.774</v>
+        <v>0.5183</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1886</v>
+        <v>0.1263</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2719</v>
+        <v>-0.3697</v>
       </c>
       <c r="E19" t="n">
-        <v>0.774</v>
+        <v>0.5183</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8343</v>
+        <v>0.6072</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0603</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8343</v>
+        <v>0.6072</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4505</v>
+        <v>0.3409</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0603</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>140</v>
@@ -1311,7 +1311,7 @@
         <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3902</v>
+        <v>0.252</v>
       </c>
       <c r="N19" t="n">
         <v>194</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3172</v>
+        <v>0.2953</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4798</v>
+        <v>-0.4713</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3172</v>
+        <v>0.2953</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3172</v>
+        <v>0.2953</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3172</v>
+        <v>0.2953</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3172</v>
+        <v>0.2953</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3172</v>
+        <v>0.2953</v>
       </c>
       <c r="N20" t="n">
         <v>139</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3062</v>
+        <v>0.2427</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0746</v>
+        <v>0.0591</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4848</v>
+        <v>-0.4952</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3062</v>
+        <v>0.2427</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3062</v>
+        <v>0.2427</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3062</v>
+        <v>0.2427</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3062</v>
+        <v>0.2427</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3062</v>
+        <v>0.2427</v>
       </c>
       <c r="N21" t="n">
         <v>143</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1076</v>
+        <v>-0.1047</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0262</v>
+        <v>-0.0255</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6732</v>
+        <v>-0.6535</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1076</v>
+        <v>-0.1047</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4089</v>
+        <v>0.3817</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5165</v>
+        <v>-0.4864</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4089</v>
+        <v>0.3817</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2208</v>
+        <v>0.2143</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5165</v>
+        <v>-0.4864</v>
       </c>
       <c r="K22" t="n">
         <v>130</v>
@@ -1449,7 +1449,7 @@
         <v>50</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2957</v>
+        <v>-0.2721</v>
       </c>
       <c r="N22" t="n">
         <v>180</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1244</v>
+        <v>-0.1062</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0303</v>
+        <v>-0.0259</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6808</v>
+        <v>-0.6542</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1244</v>
+        <v>-0.1062</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2589</v>
+        <v>-0.2196</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1345</v>
+        <v>0.1134</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2589</v>
+        <v>-0.2196</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1398</v>
+        <v>-0.1233</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1345</v>
+        <v>0.1134</v>
       </c>
       <c r="K23" t="n">
         <v>130</v>
@@ -1495,7 +1495,7 @@
         <v>50</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.005299999999999999</v>
+        <v>-0.009900000000000006</v>
       </c>
       <c r="N23" t="n">
         <v>180</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1511</v>
+        <v>-0.1521</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0368</v>
+        <v>-0.0371</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.6751</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1511</v>
+        <v>-0.1521</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1511</v>
+        <v>-0.1521</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1511</v>
+        <v>-0.1521</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1511</v>
+        <v>-0.1521</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1511</v>
+        <v>-0.1521</v>
       </c>
       <c r="N24" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1879</v>
+        <v>-0.1622</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0458</v>
+        <v>-0.0395</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7097</v>
+        <v>-0.6797</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1879</v>
+        <v>-0.1622</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1879</v>
+        <v>-0.1622</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1879</v>
+        <v>-0.1622</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1879</v>
+        <v>-0.1622</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1879</v>
+        <v>-0.1622</v>
       </c>
       <c r="N25" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9087</v>
+        <v>-0.9368</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2214</v>
+        <v>-0.2282</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.0379</v>
+        <v>-1.0325</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9087</v>
+        <v>-0.9368</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7613</v>
+        <v>-0.7438</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1474</v>
+        <v>-0.193</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7613</v>
+        <v>-0.7438</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4111</v>
+        <v>-0.4176</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1474</v>
+        <v>-0.193</v>
       </c>
       <c r="K26" t="n">
         <v>140</v>
@@ -1633,7 +1633,7 @@
         <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5585</v>
+        <v>-0.6106</v>
       </c>
       <c r="N26" t="n">
         <v>194</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.2119</v>
+        <v>-1.0629</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2952</v>
+        <v>-0.2589</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.1759</v>
+        <v>-1.09</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.2119</v>
+        <v>-1.0629</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.1802</v>
+        <v>-0.9988</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0317</v>
+        <v>-0.0641</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.1802</v>
+        <v>-0.9988</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6373</v>
+        <v>-0.5608</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0317</v>
+        <v>-0.0641</v>
       </c>
       <c r="K27" t="n">
         <v>140</v>
@@ -1679,7 +1679,7 @@
         <v>54</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6689999999999999</v>
+        <v>-0.6249</v>
       </c>
       <c r="N27" t="n">
         <v>194</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.2312</v>
+        <v>-1.2082</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2999</v>
+        <v>-0.2943</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.1847</v>
+        <v>-1.1562</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.2312</v>
+        <v>-1.2082</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.2312</v>
+        <v>-0.8424</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.3658</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.2312</v>
+        <v>-0.8424</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.2312</v>
+        <v>-0.473</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.3658</v>
       </c>
       <c r="K28" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.2312</v>
+        <v>-0.8388</v>
       </c>
       <c r="N28" t="n">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.281</v>
+        <v>-1.2252</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3121</v>
+        <v>-0.2985</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2073</v>
+        <v>-1.1639</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.281</v>
+        <v>-1.2252</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.8802</v>
+        <v>-1.2252</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4008</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.8802</v>
+        <v>-1.2252</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4753</v>
+        <v>-1.2252</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4008</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.8761</v>
+        <v>-1.2252</v>
       </c>
       <c r="N29" t="n">
-        <v>180</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.005</v>
+        <v>-1.9366</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4884</v>
+        <v>-0.4718</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.5369</v>
+        <v>-1.488</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.005</v>
+        <v>-1.9366</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.005</v>
+        <v>-1.9366</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.005</v>
+        <v>-1.9366</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.005</v>
+        <v>-1.9366</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.005</v>
+        <v>-1.9366</v>
       </c>
       <c r="N30" t="n">
         <v>143</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.5921</v>
+        <v>-2.3682</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6315</v>
+        <v>-0.5769</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.8042</v>
+        <v>-1.6846</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.5921</v>
+        <v>-2.3682</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.0497</v>
+        <v>-1.8639</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5424</v>
+        <v>-0.5043</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.0497</v>
+        <v>-1.8639</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.1068</v>
+        <v>-1.0465</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5424</v>
+        <v>-0.5043</v>
       </c>
       <c r="K31" t="n">
         <v>133</v>
@@ -1863,7 +1863,7 @@
         <v>101</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.6492</v>
+        <v>-1.5508</v>
       </c>
       <c r="N31" t="n">
         <v>234</v>
@@ -1969,10 +1969,10 @@
         <v>1.44</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0405</v>
+        <v>1.0365</v>
       </c>
       <c r="J2" t="n">
-        <v>30.1745</v>
+        <v>30.0585</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7218</v>
+        <v>0.6912</v>
       </c>
       <c r="J3" t="n">
-        <v>20.9322</v>
+        <v>20.0448</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3178</v>
+        <v>0.2834</v>
       </c>
       <c r="J4" t="n">
-        <v>9.216200000000001</v>
+        <v>8.2186</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0347</v>
+        <v>0.0246</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0063</v>
+        <v>0.7134</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.93</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2885</v>
+        <v>-0.2484</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.3665</v>
+        <v>-7.2036</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4386</v>
+        <v>0.381</v>
       </c>
       <c r="J7" t="n">
-        <v>12.7194</v>
+        <v>11.049</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3686</v>
+        <v>0.3137</v>
       </c>
       <c r="J8" t="n">
-        <v>10.6894</v>
+        <v>9.097300000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.93</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1099</v>
+        <v>-0.0925</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.1871</v>
+        <v>-2.6825</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1997</v>
+        <v>-0.1791</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.7913</v>
+        <v>-5.1939</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2896</v>
+        <v>-0.2711</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.398400000000001</v>
+        <v>-7.8619</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>2.18</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J12" t="n">
-        <v>40.5966</v>
+        <v>43.6084</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.38</v>
       </c>
       <c r="I13" t="n">
-        <v>0.877</v>
+        <v>0.8687</v>
       </c>
       <c r="J13" t="n">
-        <v>19.294</v>
+        <v>19.1114</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7227</v>
+        <v>0.7045</v>
       </c>
       <c r="J14" t="n">
-        <v>15.8994</v>
+        <v>15.499</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.24</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5744</v>
       </c>
       <c r="J15" t="n">
-        <v>13.1846</v>
+        <v>12.6368</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>1.07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1913</v>
+        <v>0.1604</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2086</v>
+        <v>3.5288</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>0.89</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1179</v>
+        <v>-0.101</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.5938</v>
+        <v>-2.222</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2079</v>
+        <v>-0.1928</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.5738</v>
+        <v>-4.2416</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3502</v>
+        <v>-0.3379</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.7044</v>
+        <v>-7.4338</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.61</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3941</v>
+        <v>-0.3834</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.670199999999999</v>
+        <v>-8.434799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.42</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5611</v>
+        <v>-0.5674</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.3442</v>
+        <v>-12.4828</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.61</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0616</v>
+        <v>1.0534</v>
       </c>
       <c r="J22" t="n">
-        <v>24.4168</v>
+        <v>24.2282</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.58</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0236</v>
+        <v>1.0145</v>
       </c>
       <c r="J23" t="n">
-        <v>23.5428</v>
+        <v>23.3335</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.44</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8427</v>
+        <v>0.8333</v>
       </c>
       <c r="J24" t="n">
-        <v>19.3821</v>
+        <v>19.1659</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.4</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7902</v>
+        <v>0.7816</v>
       </c>
       <c r="J25" t="n">
-        <v>18.1746</v>
+        <v>17.9768</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.13</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3497</v>
+        <v>0.3172</v>
       </c>
       <c r="J26" t="n">
-        <v>8.043100000000001</v>
+        <v>7.2956</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1382</v>
+        <v>-0.121</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.1786</v>
+        <v>-2.783</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2156</v>
+        <v>-0.2006</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.9588</v>
+        <v>-4.6138</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.59</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.41</v>
+        <v>-0.4004</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.43</v>
+        <v>-9.209199999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.54</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4541</v>
+        <v>-0.4476</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.4443</v>
+        <v>-10.2948</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4717</v>
+        <v>-0.4668</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.8491</v>
+        <v>-10.7364</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.72</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2505</v>
+        <v>1.2523</v>
       </c>
       <c r="J32" t="n">
-        <v>33.7635</v>
+        <v>33.8121</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4513</v>
+        <v>0.4223</v>
       </c>
       <c r="J33" t="n">
-        <v>12.1851</v>
+        <v>11.4021</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4316</v>
+        <v>0.3992</v>
       </c>
       <c r="J34" t="n">
-        <v>11.6532</v>
+        <v>10.7784</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.08</v>
       </c>
       <c r="I35" t="n">
-        <v>0.257</v>
+        <v>0.226</v>
       </c>
       <c r="J35" t="n">
-        <v>6.939</v>
+        <v>6.102</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.432</v>
+        <v>-0.3911</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.664</v>
+        <v>-10.5597</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.33</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6062</v>
+        <v>0.5802</v>
       </c>
       <c r="J37" t="n">
-        <v>16.3674</v>
+        <v>15.6654</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.92</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1187</v>
+        <v>-0.1016</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.2049</v>
+        <v>-2.7432</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.91</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1303</v>
+        <v>-0.1124</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.5181</v>
+        <v>-3.0348</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.86</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1852</v>
+        <v>-0.1652</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.0004</v>
+        <v>-4.4604</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.66</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3783</v>
+        <v>-0.3654</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.2141</v>
+        <v>-9.8658</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.75</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2557</v>
+        <v>1.2553</v>
       </c>
       <c r="J42" t="n">
-        <v>30.1368</v>
+        <v>30.1272</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.68</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1674</v>
+        <v>1.1619</v>
       </c>
       <c r="J43" t="n">
-        <v>28.0176</v>
+        <v>27.8856</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3151</v>
+        <v>0.2832</v>
       </c>
       <c r="J44" t="n">
-        <v>7.5624</v>
+        <v>6.7968</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2072</v>
+        <v>0.1778</v>
       </c>
       <c r="J45" t="n">
-        <v>4.9728</v>
+        <v>4.2672</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1161</v>
+        <v>0.0919</v>
       </c>
       <c r="J46" t="n">
-        <v>2.7864</v>
+        <v>2.2056</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>0.96</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0433</v>
+        <v>-0.0317</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.0392</v>
+        <v>-0.7608</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>0.84</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1892</v>
+        <v>-0.1735</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.5408</v>
+        <v>-4.164</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.72</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3043</v>
+        <v>-0.2885</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.3032</v>
+        <v>-6.924</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3134</v>
+        <v>-0.2978</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.5216</v>
+        <v>-7.1472</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4656</v>
+        <v>-0.4602</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.1744</v>
+        <v>-11.0448</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.52</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0195</v>
+        <v>1.0108</v>
       </c>
       <c r="J52" t="n">
-        <v>30.585</v>
+        <v>30.324</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8612</v>
+        <v>0.8464</v>
       </c>
       <c r="J53" t="n">
-        <v>25.836</v>
+        <v>25.392</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.9</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3555</v>
+        <v>-0.3128</v>
       </c>
       <c r="J54" t="n">
-        <v>-10.665</v>
+        <v>-9.384</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.8</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.5633</v>
       </c>
       <c r="J55" t="n">
-        <v>-18.039</v>
+        <v>-16.899</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8011</v>
+        <v>-0.7773</v>
       </c>
       <c r="J56" t="n">
-        <v>-24.033</v>
+        <v>-23.319</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3182</v>
+        <v>0.2672</v>
       </c>
       <c r="J57" t="n">
-        <v>9.545999999999999</v>
+        <v>8.016</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.12</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2817</v>
+        <v>0.2337</v>
       </c>
       <c r="J58" t="n">
-        <v>8.451000000000001</v>
+        <v>7.011</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.244</v>
+        <v>0.1996</v>
       </c>
       <c r="J59" t="n">
-        <v>7.32</v>
+        <v>5.988</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0622</v>
+        <v>-0.0486</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.866</v>
+        <v>-1.458</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1034</v>
+        <v>-0.0858</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.102</v>
+        <v>-2.574</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6694</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>20.082</v>
+        <v>18.342</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.02</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0717</v>
+        <v>0.0517</v>
       </c>
       <c r="J63" t="n">
-        <v>2.151</v>
+        <v>1.551</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0596</v>
+        <v>-0.0466</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.788</v>
+        <v>-1.398</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1371</v>
+        <v>-0.1178</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.113</v>
+        <v>-3.534</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2033</v>
+        <v>-0.1826</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.099</v>
+        <v>-5.478</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.27</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7138</v>
+        <v>0.6815</v>
       </c>
       <c r="J67" t="n">
-        <v>21.414</v>
+        <v>20.445</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5161</v>
+        <v>0.4765</v>
       </c>
       <c r="J68" t="n">
-        <v>15.483</v>
+        <v>14.295</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4226</v>
+        <v>0.3829</v>
       </c>
       <c r="J69" t="n">
-        <v>12.678</v>
+        <v>11.487</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.299</v>
+        <v>0.2629</v>
       </c>
       <c r="J70" t="n">
-        <v>8.970000000000001</v>
+        <v>7.887</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.584</v>
+        <v>-0.5456</v>
       </c>
       <c r="J71" t="n">
-        <v>-17.52</v>
+        <v>-16.368</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6446</v>
+        <v>0.5851</v>
       </c>
       <c r="J72" t="n">
-        <v>19.338</v>
+        <v>17.553</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.13</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2921</v>
+        <v>0.2454</v>
       </c>
       <c r="J73" t="n">
-        <v>8.763</v>
+        <v>7.362</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1352</v>
+        <v>0.1065</v>
       </c>
       <c r="J74" t="n">
-        <v>4.056</v>
+        <v>3.195</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1352</v>
+        <v>0.1065</v>
       </c>
       <c r="J75" t="n">
-        <v>4.056</v>
+        <v>3.195</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.02</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0603</v>
+        <v>0.0443</v>
       </c>
       <c r="J76" t="n">
-        <v>1.809</v>
+        <v>1.329</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.25</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4543</v>
       </c>
       <c r="J77" t="n">
-        <v>15.408</v>
+        <v>13.629</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.11</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2693</v>
+        <v>0.2215</v>
       </c>
       <c r="J78" t="n">
-        <v>8.079000000000001</v>
+        <v>6.645</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.146</v>
+        <v>0.1126</v>
       </c>
       <c r="J79" t="n">
-        <v>4.38</v>
+        <v>3.378</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1127</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.381</v>
+        <v>-2.841</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3211</v>
+        <v>-0.3045</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.632999999999999</v>
+        <v>-9.135</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5883</v>
+        <v>0.5498</v>
       </c>
       <c r="J82" t="n">
-        <v>15.8841</v>
+        <v>14.8446</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.17</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4972</v>
+        <v>0.4566</v>
       </c>
       <c r="J83" t="n">
-        <v>13.4244</v>
+        <v>12.3282</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3267</v>
+        <v>0.2884</v>
       </c>
       <c r="J84" t="n">
-        <v>8.8209</v>
+        <v>7.7868</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2193</v>
+        <v>0.187</v>
       </c>
       <c r="J85" t="n">
-        <v>5.9211</v>
+        <v>5.049</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4847</v>
+        <v>-0.4426</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.0869</v>
+        <v>-11.9502</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5868</v>
+        <v>0.5271</v>
       </c>
       <c r="J87" t="n">
-        <v>15.8436</v>
+        <v>14.2317</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2839</v>
+        <v>0.2353</v>
       </c>
       <c r="J88" t="n">
-        <v>7.6653</v>
+        <v>6.3531</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0611</v>
+        <v>-0.0478</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.6497</v>
+        <v>-1.2906</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0892</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.4084</v>
+        <v>-1.9683</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1944</v>
+        <v>-0.1738</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.2488</v>
+        <v>-4.6926</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.29</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6039</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>15.7014</v>
+        <v>14.2454</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2876</v>
+        <v>0.238</v>
       </c>
       <c r="J93" t="n">
-        <v>7.4776</v>
+        <v>6.188</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.83</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2156</v>
+        <v>-0.1954</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.6056</v>
+        <v>-5.0804</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2653</v>
+        <v>-0.2459</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.8978</v>
+        <v>-6.3934</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.63</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4044</v>
+        <v>-0.3939</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.5144</v>
+        <v>-10.2414</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0723</v>
+        <v>1.0809</v>
       </c>
       <c r="J97" t="n">
-        <v>27.8798</v>
+        <v>28.1034</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7416</v>
+        <v>0.7123</v>
       </c>
       <c r="J98" t="n">
-        <v>19.2816</v>
+        <v>18.5198</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.17</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4839</v>
+        <v>0.447</v>
       </c>
       <c r="J99" t="n">
-        <v>12.5814</v>
+        <v>11.622</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1118</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>2.9068</v>
+        <v>2.3634</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.82</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5713</v>
+        <v>-0.5335</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.8538</v>
+        <v>-13.871</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2651</v>
+        <v>-0.2514</v>
       </c>
       <c r="J102" t="n">
-        <v>-5.302</v>
+        <v>-5.028</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.7</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2956</v>
+        <v>-0.2841</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.912</v>
+        <v>-5.682</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.57</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4158</v>
+        <v>-0.4098</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.316000000000001</v>
+        <v>-8.196</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.48</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4927</v>
+        <v>-0.4906</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.853999999999999</v>
+        <v>-9.811999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.36</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5991</v>
+        <v>-0.6098</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.982</v>
+        <v>-12.196</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.93</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5952</v>
+        <v>1.6339</v>
       </c>
       <c r="J107" t="n">
-        <v>31.904</v>
+        <v>32.678</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1553</v>
+        <v>1.1721</v>
       </c>
       <c r="J108" t="n">
-        <v>23.106</v>
+        <v>23.442</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9291</v>
+        <v>0.9262</v>
       </c>
       <c r="J109" t="n">
-        <v>18.582</v>
+        <v>18.524</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.27</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6373</v>
       </c>
       <c r="J110" t="n">
-        <v>13.176</v>
+        <v>12.746</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.27</v>
+        <v>0.237</v>
       </c>
       <c r="J111" t="n">
-        <v>5.4</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.26</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5273</v>
+        <v>0.4678</v>
       </c>
       <c r="J112" t="n">
-        <v>14.7644</v>
+        <v>13.0984</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.21</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4452</v>
+        <v>0.3872</v>
       </c>
       <c r="J113" t="n">
-        <v>12.4656</v>
+        <v>10.8416</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1009</v>
+        <v>-0.0837</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.8252</v>
+        <v>-2.3436</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.87</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1823</v>
+        <v>-0.1617</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.1044</v>
+        <v>-4.5276</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2141</v>
+        <v>-0.1934</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.9948</v>
+        <v>-5.4152</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7965</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>22.302</v>
+        <v>21.5516</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.22</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6049</v>
+        <v>0.5675</v>
       </c>
       <c r="J118" t="n">
-        <v>16.9372</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3979</v>
+        <v>0.3588</v>
       </c>
       <c r="J119" t="n">
-        <v>11.1412</v>
+        <v>10.0464</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1212</v>
+        <v>0.0988</v>
       </c>
       <c r="J120" t="n">
-        <v>3.3936</v>
+        <v>2.7664</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5613</v>
+        <v>-0.522</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.7164</v>
+        <v>-14.616</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.15</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3709</v>
+        <v>0.3173</v>
       </c>
       <c r="J122" t="n">
-        <v>10.0143</v>
+        <v>8.5671</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.05</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1667</v>
+        <v>0.1295</v>
       </c>
       <c r="J123" t="n">
-        <v>4.5009</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2332</v>
+        <v>-0.2134</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.2964</v>
+        <v>-5.7618</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.77</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2724</v>
+        <v>-0.2533</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.3548</v>
+        <v>-6.8391</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3105</v>
+        <v>-0.2929</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.3835</v>
+        <v>-7.9083</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.71</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3999</v>
+        <v>1.4295</v>
       </c>
       <c r="J127" t="n">
-        <v>37.7973</v>
+        <v>38.5965</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.13</v>
       </c>
       <c r="I128" t="n">
-        <v>0.393</v>
+        <v>0.3565</v>
       </c>
       <c r="J128" t="n">
-        <v>10.611</v>
+        <v>9.625500000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1784</v>
+        <v>0.1513</v>
       </c>
       <c r="J129" t="n">
-        <v>4.8168</v>
+        <v>4.0851</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1132</v>
+        <v>0.0921</v>
       </c>
       <c r="J130" t="n">
-        <v>3.0564</v>
+        <v>2.4867</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5699</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.3873</v>
+        <v>-14.3586</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.17</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3845</v>
+        <v>0.3288</v>
       </c>
       <c r="J132" t="n">
-        <v>10.766</v>
+        <v>9.2064</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2145</v>
+        <v>0.1717</v>
       </c>
       <c r="J133" t="n">
-        <v>6.006</v>
+        <v>4.8076</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1936</v>
+        <v>0.1532</v>
       </c>
       <c r="J134" t="n">
-        <v>5.4208</v>
+        <v>4.2896</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2004</v>
+        <v>-0.1798</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.6112</v>
+        <v>-5.0344</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2807</v>
+        <v>-0.2618</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.8596</v>
+        <v>-7.3304</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.27</v>
       </c>
       <c r="I137" t="n">
-        <v>0.745</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>20.86</v>
+        <v>20.0256</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0997</v>
+        <v>0.0766</v>
       </c>
       <c r="J138" t="n">
-        <v>2.7916</v>
+        <v>2.1448</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0585</v>
+        <v>-0.0426</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.638</v>
+        <v>-1.1928</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2873</v>
+        <v>-0.2474</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.0444</v>
+        <v>-6.9272</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.61</v>
+        <v>-0.5716</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.08</v>
+        <v>-16.0048</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.69</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3572</v>
+        <v>1.3813</v>
       </c>
       <c r="J142" t="n">
-        <v>32.5728</v>
+        <v>33.1512</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4671</v>
       </c>
       <c r="J143" t="n">
-        <v>12.036</v>
+        <v>11.2104</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.08</v>
       </c>
       <c r="I144" t="n">
-        <v>0.256</v>
+        <v>0.2251</v>
       </c>
       <c r="J144" t="n">
-        <v>6.144</v>
+        <v>5.4024</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.228</v>
+        <v>0.1984</v>
       </c>
       <c r="J145" t="n">
-        <v>5.472</v>
+        <v>4.7616</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0343</v>
+        <v>-0.0287</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.8232</v>
+        <v>-0.6888</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.24</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5301</v>
+        <v>0.4742</v>
       </c>
       <c r="J147" t="n">
-        <v>12.7224</v>
+        <v>11.3808</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.89</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1503</v>
+        <v>-0.1322</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.6072</v>
+        <v>-3.1728</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.87</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1717</v>
+        <v>-0.1527</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.1208</v>
+        <v>-3.6648</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.84</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2029</v>
+        <v>-0.1832</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.8696</v>
+        <v>-4.3968</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.67</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3659</v>
+        <v>-0.3519</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.781599999999999</v>
+        <v>-8.445600000000001</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.43</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7832</v>
+        <v>0.729</v>
       </c>
       <c r="J152" t="n">
-        <v>23.496</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.15</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3385</v>
+        <v>0.2858</v>
       </c>
       <c r="J153" t="n">
-        <v>10.155</v>
+        <v>8.574</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2065</v>
+        <v>0.1658</v>
       </c>
       <c r="J154" t="n">
-        <v>6.195</v>
+        <v>4.974</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2258</v>
+        <v>-0.2054</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.774</v>
+        <v>-6.162</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3419</v>
+        <v>-0.327</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.257</v>
+        <v>-9.81</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.14</v>
       </c>
       <c r="I157" t="n">
-        <v>0.331</v>
+        <v>0.2782</v>
       </c>
       <c r="J157" t="n">
-        <v>9.93</v>
+        <v>8.346</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3125</v>
+        <v>0.2609</v>
       </c>
       <c r="J158" t="n">
-        <v>9.375</v>
+        <v>7.827</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0751</v>
+        <v>0.0534</v>
       </c>
       <c r="J159" t="n">
-        <v>2.253</v>
+        <v>1.602</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.86</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1897</v>
+        <v>-0.1691</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.691</v>
+        <v>-5.073</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.78</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2708</v>
+        <v>-0.2515</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.124000000000001</v>
+        <v>-7.545</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.797</v>
+        <v>0.7718</v>
       </c>
       <c r="J162" t="n">
-        <v>19.925</v>
+        <v>19.295</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6323</v>
+        <v>0.5991</v>
       </c>
       <c r="J163" t="n">
-        <v>15.8075</v>
+        <v>14.9775</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.19</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5253</v>
+        <v>0.49</v>
       </c>
       <c r="J164" t="n">
-        <v>13.1325</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.1</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3131</v>
+        <v>0.2798</v>
       </c>
       <c r="J165" t="n">
-        <v>7.8275</v>
+        <v>6.995</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2027</v>
+        <v>0.1743</v>
       </c>
       <c r="J166" t="n">
-        <v>5.0675</v>
+        <v>4.3575</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.48</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8739</v>
+        <v>0.8282</v>
       </c>
       <c r="J167" t="n">
-        <v>21.8475</v>
+        <v>20.705</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0815</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.4525</v>
+        <v>-2.0375</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.92</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1226</v>
+        <v>-0.1043</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.065</v>
+        <v>-2.6075</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2414</v>
+        <v>-0.2212</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.035</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2612</v>
+        <v>-0.2416</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.53</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.5</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1285</v>
+        <v>1.1423</v>
       </c>
       <c r="J172" t="n">
-        <v>33.855</v>
+        <v>34.269</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.05</v>
       </c>
       <c r="I173" t="n">
-        <v>0.186</v>
+        <v>0.1573</v>
       </c>
       <c r="J173" t="n">
-        <v>5.58</v>
+        <v>4.719</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1212</v>
+        <v>0.0988</v>
       </c>
       <c r="J174" t="n">
-        <v>3.636</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.97</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1537</v>
+        <v>-0.1225</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.611</v>
+        <v>-3.675</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1875</v>
+        <v>-0.153</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.625</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>27.384</v>
+        <v>26.085</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3818</v>
+        <v>0.3263</v>
       </c>
       <c r="J178" t="n">
-        <v>11.454</v>
+        <v>9.789</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1701</v>
+        <v>0.133</v>
       </c>
       <c r="J179" t="n">
-        <v>5.103</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.91</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1354</v>
+        <v>-0.1163</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.062</v>
+        <v>-3.489</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.35</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6465</v>
+        <v>-0.6722</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.395</v>
+        <v>-20.166</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.81</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4838</v>
+        <v>1.5152</v>
       </c>
       <c r="J182" t="n">
-        <v>35.6112</v>
+        <v>36.3648</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.33</v>
       </c>
       <c r="I183" t="n">
-        <v>0.796</v>
+        <v>0.7762</v>
       </c>
       <c r="J183" t="n">
-        <v>19.104</v>
+        <v>18.6288</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6592</v>
+        <v>0.6333</v>
       </c>
       <c r="J184" t="n">
-        <v>15.8208</v>
+        <v>15.1992</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2667</v>
+        <v>0.2358</v>
       </c>
       <c r="J185" t="n">
-        <v>6.4008</v>
+        <v>5.6592</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0866</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>2.0784</v>
+        <v>1.5768</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.06</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2149</v>
+        <v>0.1757</v>
       </c>
       <c r="J187" t="n">
-        <v>5.1576</v>
+        <v>4.2168</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>0.91</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1197</v>
+        <v>-0.1049</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.8728</v>
+        <v>-2.5176</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>0.78</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2544</v>
+        <v>-0.2363</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.1056</v>
+        <v>-5.6712</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3385</v>
+        <v>-0.3228</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.124000000000001</v>
+        <v>-7.7472</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.64</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3839</v>
+        <v>-0.3711</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.2136</v>
+        <v>-8.9064</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.48</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0622</v>
+        <v>1.0703</v>
       </c>
       <c r="J192" t="n">
-        <v>26.555</v>
+        <v>26.7575</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>1.43</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9859</v>
+        <v>0.9821</v>
       </c>
       <c r="J193" t="n">
-        <v>24.6475</v>
+        <v>24.5525</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6626</v>
+        <v>0.6353</v>
       </c>
       <c r="J194" t="n">
-        <v>16.565</v>
+        <v>15.8825</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.324</v>
+        <v>0.292</v>
       </c>
       <c r="J195" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2716</v>
+        <v>0.2406</v>
       </c>
       <c r="J196" t="n">
-        <v>6.79</v>
+        <v>6.015</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3302</v>
+        <v>0.2807</v>
       </c>
       <c r="J197" t="n">
-        <v>8.255000000000001</v>
+        <v>7.0175</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0448</v>
+        <v>-0.0356</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.12</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>0.78</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2576</v>
+        <v>-0.2388</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.44</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>0.73</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3051</v>
+        <v>-0.2876</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.6275</v>
+        <v>-7.19</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>0.65</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3786</v>
+        <v>-0.3654</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.465</v>
+        <v>-9.135</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>1.37</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9306</v>
+        <v>0.9167</v>
       </c>
       <c r="J202" t="n">
-        <v>27.918</v>
+        <v>27.501</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5693</v>
+        <v>0.5298</v>
       </c>
       <c r="J203" t="n">
-        <v>17.079</v>
+        <v>15.894</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4768</v>
+        <v>0.4355</v>
       </c>
       <c r="J204" t="n">
-        <v>14.304</v>
+        <v>13.065</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2425</v>
+        <v>-0.204</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.275</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.9267</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-27.801</v>
+        <v>-27.474</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.21</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4546</v>
+        <v>0.3966</v>
       </c>
       <c r="J207" t="n">
-        <v>13.638</v>
+        <v>11.898</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1943</v>
+        <v>0.1537</v>
       </c>
       <c r="J208" t="n">
-        <v>5.829</v>
+        <v>4.611</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>0.9</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1456</v>
+        <v>-0.1261</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.368</v>
+        <v>-3.783</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>0.88</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1679</v>
+        <v>-0.1477</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.037</v>
+        <v>-4.431</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>0.86</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1895</v>
+        <v>-0.169</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.685</v>
+        <v>-5.07</v>
       </c>
     </row>
   </sheetData>
